--- a/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\迷宫装备\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E8D2DE-B76E-416D-AB6E-F83FC7BEAE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CAE7DA-D210-4384-A06A-668354CA216B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="317">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1065,1111 +1065,6 @@
   </si>
   <si>
     <t>4:10</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击——攻击固定值和</t>
-  </si>
-  <si>
-    <t>攻击——攻击提高和，万分比</t>
-  </si>
-  <si>
-    <t>防御——防御固定值</t>
-  </si>
-  <si>
-    <t>防御——防御提高和，万分比</t>
-  </si>
-  <si>
-    <t>攻击伤害——伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>受到伤害——目标受到伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>额外伤害——额外伤害固定值和</t>
-  </si>
-  <si>
-    <t>受到额外伤害——目标额外受伤固定值和</t>
-  </si>
-  <si>
-    <t>伤害总加成——伤害总加成，万分比</t>
-  </si>
-  <si>
-    <t>受到伤害总加成——目标受伤总加成，万分比</t>
-  </si>
-  <si>
-    <t>攻击速度——攻击速度</t>
-  </si>
-  <si>
-    <t>攻击范围——攻击距离，万分比</t>
-  </si>
-  <si>
-    <t>击中怪物回血——击中怪物回血</t>
-  </si>
-  <si>
-    <t>击中回血效果——击中回血效果提高%</t>
-  </si>
-  <si>
-    <t>暴击几率——暴击几率和，万分比</t>
-  </si>
-  <si>
-    <t>暴击伤害——暴击伤害和，万分比</t>
-  </si>
-  <si>
-    <t>移动速度——移动速度，万分比</t>
-  </si>
-  <si>
-    <t>攻击数量——攻击目标的个数</t>
-  </si>
-  <si>
-    <t>持续伤害提高——无元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高——受到无元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>额外持续伤害——额外无元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>受到额外持续伤害——受到额外无元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>攻击附加冰元素——标记属性，有这个id表示攻击要额外计算冰属性公式</t>
-  </si>
-  <si>
-    <t>攻击附加冰元素系数——冰元素的转换系数，实现方式为：攻击附带额外冰元素攻击，附带的冰攻=角色攻击*冰元素系数</t>
-  </si>
-  <si>
-    <t>冰元素攻击——冰攻击固定值和</t>
-  </si>
-  <si>
-    <t>冰元素攻击——冰攻击提高和，万分比</t>
-  </si>
-  <si>
-    <t>冰元素伤害——冰伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>受到冰元素伤害——目标受到冰伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>额外冰伤害——额外冰伤害固定值和</t>
-  </si>
-  <si>
-    <t>受到额外冰伤害——目标额外受冰伤害固定值和</t>
-  </si>
-  <si>
-    <t>冰持续伤害提高——冰元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>受到冰持续伤害提高——受到冰元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>额外冰持续伤害固定值——额外冰元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>受到额外冰持续伤害固定值——受到额外冰元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>攻击附加火元素——标记属性，有这个id表示攻击要额外计算火属性公式</t>
-  </si>
-  <si>
-    <t>攻击附加火元素系数——火元素的转换系数，实现方式为：攻击附带额外火元素攻击，附带的火攻=角色攻击*火元素系数</t>
-  </si>
-  <si>
-    <t>火元素攻击——火攻击固定值和</t>
-  </si>
-  <si>
-    <t>火元素攻击——火攻击提高和，万分比</t>
-  </si>
-  <si>
-    <t>火元素伤害——火伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>受到火元素伤害——目标受到火伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>额外火伤害——额外火伤害固定值和</t>
-  </si>
-  <si>
-    <t>受到额外火伤害——目标额外受火伤害固定值和</t>
-  </si>
-  <si>
-    <t>火持续伤害提高——火元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>受到火持续伤害提高——受到火元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>额外火持续伤害固定值——额外火元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>受到额外火持续伤害固定值——受到额外火元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>攻击附加电元素——标记属性，有这个id表示攻击要额外计算电属性公式</t>
-  </si>
-  <si>
-    <t>攻击附加电元素系数——电元素的转换系数，实现方式为：攻击附带额外电元素攻击，附带的电攻=角色攻击*电元素系数</t>
-  </si>
-  <si>
-    <t>电元素攻击——电攻击固定值和</t>
-  </si>
-  <si>
-    <t>电元素攻击——电攻击提高和，万分比</t>
-  </si>
-  <si>
-    <t>电元素伤害——电伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>受到电元素伤害——目标受到电伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>额外电伤害——额外电伤害固定值和</t>
-  </si>
-  <si>
-    <t>受到额外电伤害——目标额外受电伤害固定值和</t>
-  </si>
-  <si>
-    <t>电持续伤害提高——电元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>受到电持续伤害提高——受到电元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>额外电持续伤害固定值——额外电元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>受到额外电持续伤害固定值——受到额外电元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>攻击附加毒元素——标记属性，有这个id表示攻击要额外计算毒属性公式</t>
-  </si>
-  <si>
-    <t>攻击附加毒元素系数——毒元素的转换系数，实现方式为：攻击附带额外毒元素攻击，附带的毒攻=角色攻击*毒元素系数</t>
-  </si>
-  <si>
-    <t>毒元素攻击——毒攻击固定值和</t>
-  </si>
-  <si>
-    <t>毒元素攻击——毒攻击提高和，万分比</t>
-  </si>
-  <si>
-    <t>毒元素伤害——毒伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>受到毒元素伤害——目标受到毒伤害提高和，万分比</t>
-  </si>
-  <si>
-    <t>额外毒伤害——额外毒伤害固定值和</t>
-  </si>
-  <si>
-    <t>受到额外毒伤害——目标额外受毒伤害固定值和</t>
-  </si>
-  <si>
-    <t>毒持续伤害提高——毒元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>受到毒持续伤害提高——受到毒元素持续伤害提高，万分比</t>
-  </si>
-  <si>
-    <t>额外毒持续伤害固定值——额外毒元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>受到额外毒持续伤害固定值——受到额外毒元素持续伤害，固定值</t>
-  </si>
-  <si>
-    <t>防御——防御提高%</t>
-  </si>
-  <si>
-    <t>防御——防御提高</t>
-  </si>
-  <si>
-    <t>生命上限——生命值上限提高%</t>
-  </si>
-  <si>
-    <t>生命上限——生命值上限提高</t>
-  </si>
-  <si>
-    <t>20001:1</t>
-  </si>
-  <si>
-    <t>20002:1</t>
-  </si>
-  <si>
-    <t>20003:1</t>
-  </si>
-  <si>
-    <t>20004:1</t>
-  </si>
-  <si>
-    <t>20005:1</t>
-  </si>
-  <si>
-    <t>20006:1</t>
-  </si>
-  <si>
-    <t>20007:1</t>
-  </si>
-  <si>
-    <t>20008:1</t>
-  </si>
-  <si>
-    <t>20009:1</t>
-  </si>
-  <si>
-    <t>20010:1</t>
-  </si>
-  <si>
-    <t>20011:1</t>
-  </si>
-  <si>
-    <t>20012:1</t>
-  </si>
-  <si>
-    <t>20013:1</t>
-  </si>
-  <si>
-    <t>20014:1</t>
-  </si>
-  <si>
-    <t>20015:1</t>
-  </si>
-  <si>
-    <t>20016:1</t>
-  </si>
-  <si>
-    <t>20017:1</t>
-  </si>
-  <si>
-    <t>20018:1</t>
-  </si>
-  <si>
-    <t>20019:1</t>
-  </si>
-  <si>
-    <t>20020:1</t>
-  </si>
-  <si>
-    <t>20021:1</t>
-  </si>
-  <si>
-    <t>20022:1</t>
-  </si>
-  <si>
-    <t>20023:1</t>
-  </si>
-  <si>
-    <t>20024:1</t>
-  </si>
-  <si>
-    <t>20025:1</t>
-  </si>
-  <si>
-    <t>20026:1</t>
-  </si>
-  <si>
-    <t>20027:1</t>
-  </si>
-  <si>
-    <t>20028:1</t>
-  </si>
-  <si>
-    <t>20029:1</t>
-  </si>
-  <si>
-    <t>20030:1</t>
-  </si>
-  <si>
-    <t>20031:1</t>
-  </si>
-  <si>
-    <t>20032:1</t>
-  </si>
-  <si>
-    <t>20033:1</t>
-  </si>
-  <si>
-    <t>20034:1</t>
-  </si>
-  <si>
-    <t>20035:1</t>
-  </si>
-  <si>
-    <t>20036:1</t>
-  </si>
-  <si>
-    <t>20037:1</t>
-  </si>
-  <si>
-    <t>20038:1</t>
-  </si>
-  <si>
-    <t>20039:1</t>
-  </si>
-  <si>
-    <t>20040:1</t>
-  </si>
-  <si>
-    <t>20041:1</t>
-  </si>
-  <si>
-    <t>20042:1</t>
-  </si>
-  <si>
-    <t>20043:1</t>
-  </si>
-  <si>
-    <t>20044:1</t>
-  </si>
-  <si>
-    <t>20045:1</t>
-  </si>
-  <si>
-    <t>20046:1</t>
-  </si>
-  <si>
-    <t>20047:1</t>
-  </si>
-  <si>
-    <t>20048:1</t>
-  </si>
-  <si>
-    <t>20049:1</t>
-  </si>
-  <si>
-    <t>20050:1</t>
-  </si>
-  <si>
-    <t>20051:1</t>
-  </si>
-  <si>
-    <t>20052:1</t>
-  </si>
-  <si>
-    <t>20053:1</t>
-  </si>
-  <si>
-    <t>20054:1</t>
-  </si>
-  <si>
-    <t>20055:1</t>
-  </si>
-  <si>
-    <t>20056:1</t>
-  </si>
-  <si>
-    <t>20057:1</t>
-  </si>
-  <si>
-    <t>20058:1</t>
-  </si>
-  <si>
-    <t>20059:1</t>
-  </si>
-  <si>
-    <t>20060:1</t>
-  </si>
-  <si>
-    <t>20061:1</t>
-  </si>
-  <si>
-    <t>20062:1</t>
-  </si>
-  <si>
-    <t>20063:1</t>
-  </si>
-  <si>
-    <t>20064:1</t>
-  </si>
-  <si>
-    <t>20065:1</t>
-  </si>
-  <si>
-    <t>20066:1</t>
-  </si>
-  <si>
-    <t>20067:1</t>
-  </si>
-  <si>
-    <t>20068:1</t>
-  </si>
-  <si>
-    <t>20069:1</t>
-  </si>
-  <si>
-    <t>20070:1</t>
-  </si>
-  <si>
-    <t>20071:1</t>
-  </si>
-  <si>
-    <t>20072:1</t>
-  </si>
-  <si>
-    <t>20073:1</t>
-  </si>
-  <si>
-    <t>20074:1</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:11</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:11</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:3</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:12</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:12</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:4</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:13</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:13</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:5</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:14</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:14</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:6</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:15</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:15</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:7</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:16</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:16</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:8</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:17</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:17</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:9</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:18</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:18</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:10</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:19</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:19</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:11</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:20</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:20</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:12</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:21</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:21</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:13</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:22</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:22</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:14</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:23</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:23</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:15</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:24</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:24</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:16</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:25</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:25</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:17</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:26</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:26</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:18</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:27</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:27</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:19</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:28</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:28</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:20</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:29</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:29</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:21</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:30</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:30</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:22</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:31</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:31</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:23</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:32</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:32</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:24</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:33</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:33</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:25</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:34</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:34</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:26</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:35</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:35</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:27</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:36</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:36</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:28</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:37</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:37</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:29</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:38</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:38</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:30</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:39</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:39</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:31</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:40</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:40</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:32</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:41</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:41</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:33</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:42</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:42</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:34</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:43</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:43</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:35</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:44</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:44</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:36</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:45</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:45</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:37</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:46</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:46</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:38</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:47</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:47</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:39</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:48</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:48</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:40</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:49</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:49</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:41</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:50</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:50</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:42</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:51</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:51</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:43</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:52</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:52</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:44</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:53</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:53</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:45</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:54</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:54</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:46</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:55</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:55</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:47</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:56</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:56</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:48</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:57</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:57</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:49</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:58</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:58</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:50</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:59</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:59</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:51</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:60</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:60</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:52</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:61</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:61</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:53</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:62</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:62</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:54</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:63</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:63</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:55</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:64</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:64</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:56</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:65</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:65</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:57</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:66</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:66</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:58</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:67</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:67</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:59</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:68</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:68</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:60</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:69</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:69</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:61</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:70</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:70</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:62</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:71</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:71</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:63</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:72</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:72</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:64</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:73</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:73</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:65</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:74</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:74</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:66</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:75</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:75</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:67</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:76</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:76</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:68</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:77</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:77</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:69</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:78</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:78</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:70</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:79</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:79</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:71</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:80</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:80</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:72</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:81</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:81</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:73</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:82</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:82</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:74</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:83</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:83</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:75</t>
-  </si>
-  <si>
-    <t>1001112:1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2651,7 +1546,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N213"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -8747,3262 +7642,6 @@
         <v>314</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A140">
-        <v>20001</v>
-      </c>
-      <c r="B140" t="s">
-        <v>317</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E140" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F140" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="G140" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="H140" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I140" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J140" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K140" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L140" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="M140" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="N140" s="24" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A141">
-        <v>20002</v>
-      </c>
-      <c r="B141" t="s">
-        <v>318</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D141" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E141" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F141" t="s">
-        <v>392</v>
-      </c>
-      <c r="G141" t="s">
-        <v>392</v>
-      </c>
-      <c r="H141" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I141" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J141" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K141" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L141" s="24" t="s">
-        <v>465</v>
-      </c>
-      <c r="M141" s="24" t="s">
-        <v>466</v>
-      </c>
-      <c r="N141" s="24" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A142">
-        <v>20003</v>
-      </c>
-      <c r="B142" t="s">
-        <v>319</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D142" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E142" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F142" t="s">
-        <v>393</v>
-      </c>
-      <c r="G142" t="s">
-        <v>393</v>
-      </c>
-      <c r="H142" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I142" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J142" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K142" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L142" s="24" t="s">
-        <v>468</v>
-      </c>
-      <c r="M142" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="N142" s="24" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A143">
-        <v>20004</v>
-      </c>
-      <c r="B143" t="s">
-        <v>320</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E143" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F143" t="s">
-        <v>394</v>
-      </c>
-      <c r="G143" t="s">
-        <v>394</v>
-      </c>
-      <c r="H143" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I143" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J143" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K143" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L143" s="24" t="s">
-        <v>471</v>
-      </c>
-      <c r="M143" s="24" t="s">
-        <v>472</v>
-      </c>
-      <c r="N143" s="24" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A144">
-        <v>20005</v>
-      </c>
-      <c r="B144" t="s">
-        <v>321</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D144" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E144" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F144" t="s">
-        <v>395</v>
-      </c>
-      <c r="G144" t="s">
-        <v>395</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I144" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J144" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K144" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L144" s="24" t="s">
-        <v>474</v>
-      </c>
-      <c r="M144" s="24" t="s">
-        <v>475</v>
-      </c>
-      <c r="N144" s="24" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A145">
-        <v>20006</v>
-      </c>
-      <c r="B145" t="s">
-        <v>322</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D145" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E145" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F145" t="s">
-        <v>396</v>
-      </c>
-      <c r="G145" t="s">
-        <v>396</v>
-      </c>
-      <c r="H145" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I145" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J145" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K145" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L145" s="24" t="s">
-        <v>477</v>
-      </c>
-      <c r="M145" s="24" t="s">
-        <v>478</v>
-      </c>
-      <c r="N145" s="24" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A146">
-        <v>20007</v>
-      </c>
-      <c r="B146" t="s">
-        <v>323</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E146" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F146" t="s">
-        <v>397</v>
-      </c>
-      <c r="G146" t="s">
-        <v>397</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I146" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J146" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K146" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L146" s="24" t="s">
-        <v>480</v>
-      </c>
-      <c r="M146" s="24" t="s">
-        <v>481</v>
-      </c>
-      <c r="N146" s="24" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A147">
-        <v>20008</v>
-      </c>
-      <c r="B147" t="s">
-        <v>324</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E147" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F147" t="s">
-        <v>398</v>
-      </c>
-      <c r="G147" t="s">
-        <v>398</v>
-      </c>
-      <c r="H147" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J147" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K147" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L147" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="M147" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="N147" s="24" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A148">
-        <v>20009</v>
-      </c>
-      <c r="B148" t="s">
-        <v>325</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D148" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E148" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F148" t="s">
-        <v>399</v>
-      </c>
-      <c r="G148" t="s">
-        <v>399</v>
-      </c>
-      <c r="H148" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J148" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K148" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L148" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="M148" s="24" t="s">
-        <v>487</v>
-      </c>
-      <c r="N148" s="24" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A149">
-        <v>20010</v>
-      </c>
-      <c r="B149" t="s">
-        <v>326</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D149" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E149" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F149" t="s">
-        <v>400</v>
-      </c>
-      <c r="G149" t="s">
-        <v>400</v>
-      </c>
-      <c r="H149" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I149" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J149" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L149" s="24" t="s">
-        <v>489</v>
-      </c>
-      <c r="M149" s="24" t="s">
-        <v>490</v>
-      </c>
-      <c r="N149" s="24" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A150">
-        <v>20011</v>
-      </c>
-      <c r="B150" t="s">
-        <v>327</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D150" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E150" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F150" t="s">
-        <v>401</v>
-      </c>
-      <c r="G150" t="s">
-        <v>401</v>
-      </c>
-      <c r="H150" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I150" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J150" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K150" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L150" s="24" t="s">
-        <v>492</v>
-      </c>
-      <c r="M150" s="24" t="s">
-        <v>493</v>
-      </c>
-      <c r="N150" s="24" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A151">
-        <v>20012</v>
-      </c>
-      <c r="B151" t="s">
-        <v>328</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D151" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E151" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F151" t="s">
-        <v>402</v>
-      </c>
-      <c r="G151" t="s">
-        <v>402</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I151" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J151" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K151" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L151" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="M151" s="24" t="s">
-        <v>496</v>
-      </c>
-      <c r="N151" s="24" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A152">
-        <v>20013</v>
-      </c>
-      <c r="B152" t="s">
-        <v>329</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D152" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E152" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F152" t="s">
-        <v>403</v>
-      </c>
-      <c r="G152" t="s">
-        <v>403</v>
-      </c>
-      <c r="H152" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I152" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J152" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K152" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L152" s="24" t="s">
-        <v>498</v>
-      </c>
-      <c r="M152" s="24" t="s">
-        <v>499</v>
-      </c>
-      <c r="N152" s="24" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A153">
-        <v>20014</v>
-      </c>
-      <c r="B153" t="s">
-        <v>330</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D153" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E153" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F153" t="s">
-        <v>404</v>
-      </c>
-      <c r="G153" t="s">
-        <v>404</v>
-      </c>
-      <c r="H153" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I153" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J153" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K153" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L153" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="M153" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="N153" s="24" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A154">
-        <v>20015</v>
-      </c>
-      <c r="B154" t="s">
-        <v>331</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D154" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E154" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F154" t="s">
-        <v>405</v>
-      </c>
-      <c r="G154" t="s">
-        <v>405</v>
-      </c>
-      <c r="H154" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J154" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K154" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L154" s="24" t="s">
-        <v>504</v>
-      </c>
-      <c r="M154" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="N154" s="24" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A155">
-        <v>20016</v>
-      </c>
-      <c r="B155" t="s">
-        <v>332</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E155" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F155" t="s">
-        <v>406</v>
-      </c>
-      <c r="G155" t="s">
-        <v>406</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I155" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J155" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K155" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L155" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="M155" s="24" t="s">
-        <v>508</v>
-      </c>
-      <c r="N155" s="24" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A156">
-        <v>20017</v>
-      </c>
-      <c r="B156" t="s">
-        <v>333</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D156" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E156" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F156" t="s">
-        <v>407</v>
-      </c>
-      <c r="G156" t="s">
-        <v>407</v>
-      </c>
-      <c r="H156" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I156" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J156" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K156" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L156" s="24" t="s">
-        <v>510</v>
-      </c>
-      <c r="M156" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="N156" s="24" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A157">
-        <v>20018</v>
-      </c>
-      <c r="B157" t="s">
-        <v>334</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E157" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F157" t="s">
-        <v>408</v>
-      </c>
-      <c r="G157" t="s">
-        <v>408</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I157" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J157" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K157" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L157" s="24" t="s">
-        <v>513</v>
-      </c>
-      <c r="M157" s="24" t="s">
-        <v>514</v>
-      </c>
-      <c r="N157" s="24" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A158">
-        <v>20019</v>
-      </c>
-      <c r="B158" t="s">
-        <v>335</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E158" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F158" t="s">
-        <v>409</v>
-      </c>
-      <c r="G158" t="s">
-        <v>409</v>
-      </c>
-      <c r="H158" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I158" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J158" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K158" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L158" s="24" t="s">
-        <v>516</v>
-      </c>
-      <c r="M158" s="24" t="s">
-        <v>517</v>
-      </c>
-      <c r="N158" s="24" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A159">
-        <v>20020</v>
-      </c>
-      <c r="B159" t="s">
-        <v>336</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D159" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E159" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F159" t="s">
-        <v>410</v>
-      </c>
-      <c r="G159" t="s">
-        <v>410</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J159" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K159" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L159" s="24" t="s">
-        <v>519</v>
-      </c>
-      <c r="M159" s="24" t="s">
-        <v>520</v>
-      </c>
-      <c r="N159" s="24" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A160">
-        <v>20021</v>
-      </c>
-      <c r="B160" t="s">
-        <v>337</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D160" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E160" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F160" t="s">
-        <v>411</v>
-      </c>
-      <c r="G160" t="s">
-        <v>411</v>
-      </c>
-      <c r="H160" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I160" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J160" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K160" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L160" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="M160" s="24" t="s">
-        <v>523</v>
-      </c>
-      <c r="N160" s="24" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A161">
-        <v>20022</v>
-      </c>
-      <c r="B161" t="s">
-        <v>338</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D161" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E161" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F161" t="s">
-        <v>412</v>
-      </c>
-      <c r="G161" t="s">
-        <v>412</v>
-      </c>
-      <c r="H161" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I161" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J161" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K161" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L161" s="24" t="s">
-        <v>525</v>
-      </c>
-      <c r="M161" s="24" t="s">
-        <v>526</v>
-      </c>
-      <c r="N161" s="24" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A162">
-        <v>20023</v>
-      </c>
-      <c r="B162" t="s">
-        <v>339</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E162" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F162" t="s">
-        <v>413</v>
-      </c>
-      <c r="G162" t="s">
-        <v>413</v>
-      </c>
-      <c r="H162" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I162" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J162" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K162" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L162" s="24" t="s">
-        <v>528</v>
-      </c>
-      <c r="M162" s="24" t="s">
-        <v>529</v>
-      </c>
-      <c r="N162" s="24" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A163">
-        <v>20024</v>
-      </c>
-      <c r="B163" t="s">
-        <v>340</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E163" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F163" t="s">
-        <v>414</v>
-      </c>
-      <c r="G163" t="s">
-        <v>414</v>
-      </c>
-      <c r="H163" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I163" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J163" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K163" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L163" s="24" t="s">
-        <v>531</v>
-      </c>
-      <c r="M163" s="24" t="s">
-        <v>532</v>
-      </c>
-      <c r="N163" s="24" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A164">
-        <v>20025</v>
-      </c>
-      <c r="B164" t="s">
-        <v>341</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D164" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E164" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F164" t="s">
-        <v>415</v>
-      </c>
-      <c r="G164" t="s">
-        <v>415</v>
-      </c>
-      <c r="H164" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I164" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J164" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K164" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L164" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="M164" s="24" t="s">
-        <v>535</v>
-      </c>
-      <c r="N164" s="24" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A165">
-        <v>20026</v>
-      </c>
-      <c r="B165" t="s">
-        <v>342</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D165" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E165" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F165" t="s">
-        <v>416</v>
-      </c>
-      <c r="G165" t="s">
-        <v>416</v>
-      </c>
-      <c r="H165" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I165" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J165" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K165" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L165" s="24" t="s">
-        <v>537</v>
-      </c>
-      <c r="M165" s="24" t="s">
-        <v>538</v>
-      </c>
-      <c r="N165" s="24" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A166">
-        <v>20027</v>
-      </c>
-      <c r="B166" t="s">
-        <v>343</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D166" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E166" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F166" t="s">
-        <v>417</v>
-      </c>
-      <c r="G166" t="s">
-        <v>417</v>
-      </c>
-      <c r="H166" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I166" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J166" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K166" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L166" s="24" t="s">
-        <v>540</v>
-      </c>
-      <c r="M166" s="24" t="s">
-        <v>541</v>
-      </c>
-      <c r="N166" s="24" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A167">
-        <v>20028</v>
-      </c>
-      <c r="B167" t="s">
-        <v>344</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E167" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F167" t="s">
-        <v>418</v>
-      </c>
-      <c r="G167" t="s">
-        <v>418</v>
-      </c>
-      <c r="H167" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I167" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J167" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K167" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L167" s="24" t="s">
-        <v>543</v>
-      </c>
-      <c r="M167" s="24" t="s">
-        <v>544</v>
-      </c>
-      <c r="N167" s="24" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A168">
-        <v>20029</v>
-      </c>
-      <c r="B168" t="s">
-        <v>345</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D168" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E168" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G168" t="s">
-        <v>419</v>
-      </c>
-      <c r="H168" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I168" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J168" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K168" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L168" s="24" t="s">
-        <v>546</v>
-      </c>
-      <c r="M168" s="24" t="s">
-        <v>547</v>
-      </c>
-      <c r="N168" s="24" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A169">
-        <v>20030</v>
-      </c>
-      <c r="B169" t="s">
-        <v>346</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D169" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E169" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F169" t="s">
-        <v>420</v>
-      </c>
-      <c r="G169" t="s">
-        <v>420</v>
-      </c>
-      <c r="H169" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I169" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J169" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K169" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L169" s="24" t="s">
-        <v>549</v>
-      </c>
-      <c r="M169" s="24" t="s">
-        <v>550</v>
-      </c>
-      <c r="N169" s="24" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A170">
-        <v>20031</v>
-      </c>
-      <c r="B170" t="s">
-        <v>347</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D170" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E170" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F170" t="s">
-        <v>421</v>
-      </c>
-      <c r="G170" t="s">
-        <v>421</v>
-      </c>
-      <c r="H170" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I170" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J170" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K170" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L170" s="24" t="s">
-        <v>552</v>
-      </c>
-      <c r="M170" s="24" t="s">
-        <v>553</v>
-      </c>
-      <c r="N170" s="24" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A171">
-        <v>20032</v>
-      </c>
-      <c r="B171" t="s">
-        <v>348</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D171" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E171" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F171" t="s">
-        <v>422</v>
-      </c>
-      <c r="G171" t="s">
-        <v>422</v>
-      </c>
-      <c r="H171" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I171" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J171" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K171" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L171" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="M171" s="24" t="s">
-        <v>556</v>
-      </c>
-      <c r="N171" s="24" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A172">
-        <v>20033</v>
-      </c>
-      <c r="B172" t="s">
-        <v>349</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D172" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E172" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F172" t="s">
-        <v>423</v>
-      </c>
-      <c r="G172" t="s">
-        <v>423</v>
-      </c>
-      <c r="H172" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J172" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K172" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L172" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="M172" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="N172" s="24" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A173">
-        <v>20034</v>
-      </c>
-      <c r="B173" t="s">
-        <v>350</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D173" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E173" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F173" t="s">
-        <v>424</v>
-      </c>
-      <c r="G173" t="s">
-        <v>424</v>
-      </c>
-      <c r="H173" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I173" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J173" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K173" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L173" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="M173" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="N173" s="24" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A174">
-        <v>20035</v>
-      </c>
-      <c r="B174" t="s">
-        <v>351</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E174" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F174" t="s">
-        <v>425</v>
-      </c>
-      <c r="G174" t="s">
-        <v>425</v>
-      </c>
-      <c r="H174" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I174" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J174" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K174" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L174" s="24" t="s">
-        <v>564</v>
-      </c>
-      <c r="M174" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="N174" s="24" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A175">
-        <v>20036</v>
-      </c>
-      <c r="B175" t="s">
-        <v>352</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D175" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E175" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F175" t="s">
-        <v>426</v>
-      </c>
-      <c r="G175" t="s">
-        <v>426</v>
-      </c>
-      <c r="H175" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I175" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J175" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K175" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L175" s="24" t="s">
-        <v>567</v>
-      </c>
-      <c r="M175" s="24" t="s">
-        <v>568</v>
-      </c>
-      <c r="N175" s="24" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A176">
-        <v>20037</v>
-      </c>
-      <c r="B176" t="s">
-        <v>353</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D176" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E176" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F176" t="s">
-        <v>427</v>
-      </c>
-      <c r="G176" t="s">
-        <v>427</v>
-      </c>
-      <c r="H176" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I176" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J176" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K176" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L176" s="24" t="s">
-        <v>570</v>
-      </c>
-      <c r="M176" s="24" t="s">
-        <v>571</v>
-      </c>
-      <c r="N176" s="24" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A177">
-        <v>20038</v>
-      </c>
-      <c r="B177" t="s">
-        <v>354</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D177" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E177" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F177" t="s">
-        <v>428</v>
-      </c>
-      <c r="G177" t="s">
-        <v>428</v>
-      </c>
-      <c r="H177" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I177" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J177" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K177" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L177" s="24" t="s">
-        <v>573</v>
-      </c>
-      <c r="M177" s="24" t="s">
-        <v>574</v>
-      </c>
-      <c r="N177" s="24" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A178">
-        <v>20039</v>
-      </c>
-      <c r="B178" t="s">
-        <v>355</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D178" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E178" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F178" t="s">
-        <v>429</v>
-      </c>
-      <c r="G178" t="s">
-        <v>429</v>
-      </c>
-      <c r="H178" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I178" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J178" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K178" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L178" s="24" t="s">
-        <v>576</v>
-      </c>
-      <c r="M178" s="24" t="s">
-        <v>577</v>
-      </c>
-      <c r="N178" s="24" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A179">
-        <v>20040</v>
-      </c>
-      <c r="B179" t="s">
-        <v>356</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D179" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E179" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F179" t="s">
-        <v>430</v>
-      </c>
-      <c r="G179" t="s">
-        <v>430</v>
-      </c>
-      <c r="H179" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J179" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K179" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L179" s="24" t="s">
-        <v>579</v>
-      </c>
-      <c r="M179" s="24" t="s">
-        <v>580</v>
-      </c>
-      <c r="N179" s="24" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A180">
-        <v>20041</v>
-      </c>
-      <c r="B180" t="s">
-        <v>357</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E180" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F180" t="s">
-        <v>431</v>
-      </c>
-      <c r="G180" t="s">
-        <v>431</v>
-      </c>
-      <c r="H180" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J180" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K180" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L180" s="24" t="s">
-        <v>582</v>
-      </c>
-      <c r="M180" s="24" t="s">
-        <v>583</v>
-      </c>
-      <c r="N180" s="24" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A181">
-        <v>20042</v>
-      </c>
-      <c r="B181" t="s">
-        <v>358</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D181" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E181" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F181" t="s">
-        <v>432</v>
-      </c>
-      <c r="G181" t="s">
-        <v>432</v>
-      </c>
-      <c r="H181" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I181" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J181" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K181" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L181" s="24" t="s">
-        <v>585</v>
-      </c>
-      <c r="M181" s="24" t="s">
-        <v>586</v>
-      </c>
-      <c r="N181" s="24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A182">
-        <v>20043</v>
-      </c>
-      <c r="B182" t="s">
-        <v>359</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D182" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E182" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F182" t="s">
-        <v>433</v>
-      </c>
-      <c r="G182" t="s">
-        <v>433</v>
-      </c>
-      <c r="H182" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I182" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J182" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K182" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L182" s="24" t="s">
-        <v>588</v>
-      </c>
-      <c r="M182" s="24" t="s">
-        <v>589</v>
-      </c>
-      <c r="N182" s="24" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A183">
-        <v>20044</v>
-      </c>
-      <c r="B183" t="s">
-        <v>360</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D183" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E183" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F183" t="s">
-        <v>434</v>
-      </c>
-      <c r="G183" t="s">
-        <v>434</v>
-      </c>
-      <c r="H183" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I183" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J183" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K183" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L183" s="24" t="s">
-        <v>591</v>
-      </c>
-      <c r="M183" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="N183" s="24" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A184">
-        <v>20045</v>
-      </c>
-      <c r="B184" t="s">
-        <v>361</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D184" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E184" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F184" t="s">
-        <v>435</v>
-      </c>
-      <c r="G184" t="s">
-        <v>435</v>
-      </c>
-      <c r="H184" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I184" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J184" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K184" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L184" s="24" t="s">
-        <v>594</v>
-      </c>
-      <c r="M184" s="24" t="s">
-        <v>595</v>
-      </c>
-      <c r="N184" s="24" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A185">
-        <v>20046</v>
-      </c>
-      <c r="B185" t="s">
-        <v>362</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D185" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E185" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F185" t="s">
-        <v>436</v>
-      </c>
-      <c r="G185" t="s">
-        <v>436</v>
-      </c>
-      <c r="H185" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I185" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J185" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K185" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L185" s="24" t="s">
-        <v>597</v>
-      </c>
-      <c r="M185" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="N185" s="24" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A186">
-        <v>20047</v>
-      </c>
-      <c r="B186" t="s">
-        <v>363</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D186" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E186" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F186" t="s">
-        <v>437</v>
-      </c>
-      <c r="G186" t="s">
-        <v>437</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I186" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J186" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K186" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L186" s="24" t="s">
-        <v>600</v>
-      </c>
-      <c r="M186" s="24" t="s">
-        <v>601</v>
-      </c>
-      <c r="N186" s="24" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A187">
-        <v>20048</v>
-      </c>
-      <c r="B187" t="s">
-        <v>364</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D187" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E187" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F187" t="s">
-        <v>438</v>
-      </c>
-      <c r="G187" t="s">
-        <v>438</v>
-      </c>
-      <c r="H187" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I187" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J187" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K187" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L187" s="24" t="s">
-        <v>603</v>
-      </c>
-      <c r="M187" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="N187" s="24" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A188">
-        <v>20049</v>
-      </c>
-      <c r="B188" t="s">
-        <v>365</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D188" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E188" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F188" t="s">
-        <v>439</v>
-      </c>
-      <c r="G188" t="s">
-        <v>439</v>
-      </c>
-      <c r="H188" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I188" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J188" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K188" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L188" s="24" t="s">
-        <v>606</v>
-      </c>
-      <c r="M188" s="24" t="s">
-        <v>607</v>
-      </c>
-      <c r="N188" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A189">
-        <v>20050</v>
-      </c>
-      <c r="B189" t="s">
-        <v>366</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D189" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E189" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F189" t="s">
-        <v>440</v>
-      </c>
-      <c r="G189" t="s">
-        <v>440</v>
-      </c>
-      <c r="H189" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I189" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J189" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K189" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L189" s="24" t="s">
-        <v>609</v>
-      </c>
-      <c r="M189" s="24" t="s">
-        <v>610</v>
-      </c>
-      <c r="N189" s="24" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A190">
-        <v>20051</v>
-      </c>
-      <c r="B190" t="s">
-        <v>367</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D190" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E190" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F190" t="s">
-        <v>441</v>
-      </c>
-      <c r="G190" t="s">
-        <v>441</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I190" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J190" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K190" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L190" s="24" t="s">
-        <v>612</v>
-      </c>
-      <c r="M190" s="24" t="s">
-        <v>613</v>
-      </c>
-      <c r="N190" s="24" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A191">
-        <v>20052</v>
-      </c>
-      <c r="B191" t="s">
-        <v>368</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D191" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E191" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F191" t="s">
-        <v>442</v>
-      </c>
-      <c r="G191" t="s">
-        <v>442</v>
-      </c>
-      <c r="H191" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I191" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J191" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K191" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L191" s="24" t="s">
-        <v>615</v>
-      </c>
-      <c r="M191" s="24" t="s">
-        <v>616</v>
-      </c>
-      <c r="N191" s="24" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A192">
-        <v>20053</v>
-      </c>
-      <c r="B192" t="s">
-        <v>369</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D192" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E192" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F192" t="s">
-        <v>443</v>
-      </c>
-      <c r="G192" t="s">
-        <v>443</v>
-      </c>
-      <c r="H192" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J192" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K192" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L192" s="24" t="s">
-        <v>618</v>
-      </c>
-      <c r="M192" s="24" t="s">
-        <v>619</v>
-      </c>
-      <c r="N192" s="24" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A193">
-        <v>20054</v>
-      </c>
-      <c r="B193" t="s">
-        <v>370</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D193" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E193" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F193" t="s">
-        <v>444</v>
-      </c>
-      <c r="G193" t="s">
-        <v>444</v>
-      </c>
-      <c r="H193" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I193" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J193" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K193" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L193" s="24" t="s">
-        <v>621</v>
-      </c>
-      <c r="M193" s="24" t="s">
-        <v>622</v>
-      </c>
-      <c r="N193" s="24" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A194">
-        <v>20055</v>
-      </c>
-      <c r="B194" t="s">
-        <v>371</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D194" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E194" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F194" t="s">
-        <v>445</v>
-      </c>
-      <c r="G194" t="s">
-        <v>445</v>
-      </c>
-      <c r="H194" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I194" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J194" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K194" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L194" s="24" t="s">
-        <v>624</v>
-      </c>
-      <c r="M194" s="24" t="s">
-        <v>625</v>
-      </c>
-      <c r="N194" s="24" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A195">
-        <v>20056</v>
-      </c>
-      <c r="B195" t="s">
-        <v>372</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D195" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E195" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F195" t="s">
-        <v>446</v>
-      </c>
-      <c r="G195" t="s">
-        <v>446</v>
-      </c>
-      <c r="H195" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I195" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J195" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K195" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L195" s="24" t="s">
-        <v>627</v>
-      </c>
-      <c r="M195" s="24" t="s">
-        <v>628</v>
-      </c>
-      <c r="N195" s="24" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A196">
-        <v>20057</v>
-      </c>
-      <c r="B196" t="s">
-        <v>373</v>
-      </c>
-      <c r="C196" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D196" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E196" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F196" t="s">
-        <v>447</v>
-      </c>
-      <c r="G196" t="s">
-        <v>447</v>
-      </c>
-      <c r="H196" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I196" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J196" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K196" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L196" s="24" t="s">
-        <v>630</v>
-      </c>
-      <c r="M196" s="24" t="s">
-        <v>631</v>
-      </c>
-      <c r="N196" s="24" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A197">
-        <v>20058</v>
-      </c>
-      <c r="B197" t="s">
-        <v>374</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D197" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E197" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F197" t="s">
-        <v>448</v>
-      </c>
-      <c r="G197" t="s">
-        <v>448</v>
-      </c>
-      <c r="H197" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I197" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J197" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K197" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L197" s="24" t="s">
-        <v>633</v>
-      </c>
-      <c r="M197" s="24" t="s">
-        <v>634</v>
-      </c>
-      <c r="N197" s="24" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A198">
-        <v>20059</v>
-      </c>
-      <c r="B198" t="s">
-        <v>375</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D198" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E198" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F198" t="s">
-        <v>449</v>
-      </c>
-      <c r="G198" t="s">
-        <v>449</v>
-      </c>
-      <c r="H198" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I198" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J198" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K198" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L198" s="24" t="s">
-        <v>636</v>
-      </c>
-      <c r="M198" s="24" t="s">
-        <v>637</v>
-      </c>
-      <c r="N198" s="24" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A199">
-        <v>20060</v>
-      </c>
-      <c r="B199" t="s">
-        <v>376</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D199" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E199" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F199" t="s">
-        <v>450</v>
-      </c>
-      <c r="G199" t="s">
-        <v>450</v>
-      </c>
-      <c r="H199" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I199" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J199" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K199" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L199" s="24" t="s">
-        <v>639</v>
-      </c>
-      <c r="M199" s="24" t="s">
-        <v>640</v>
-      </c>
-      <c r="N199" s="24" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A200">
-        <v>20061</v>
-      </c>
-      <c r="B200" t="s">
-        <v>377</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D200" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E200" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F200" t="s">
-        <v>451</v>
-      </c>
-      <c r="G200" t="s">
-        <v>451</v>
-      </c>
-      <c r="H200" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I200" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J200" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K200" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L200" s="24" t="s">
-        <v>642</v>
-      </c>
-      <c r="M200" s="24" t="s">
-        <v>643</v>
-      </c>
-      <c r="N200" s="24" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A201">
-        <v>20062</v>
-      </c>
-      <c r="B201" t="s">
-        <v>378</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D201" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E201" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F201" t="s">
-        <v>452</v>
-      </c>
-      <c r="G201" t="s">
-        <v>452</v>
-      </c>
-      <c r="H201" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I201" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J201" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K201" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L201" s="24" t="s">
-        <v>645</v>
-      </c>
-      <c r="M201" s="24" t="s">
-        <v>646</v>
-      </c>
-      <c r="N201" s="24" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A202">
-        <v>20063</v>
-      </c>
-      <c r="B202" t="s">
-        <v>379</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D202" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E202" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F202" t="s">
-        <v>453</v>
-      </c>
-      <c r="G202" t="s">
-        <v>453</v>
-      </c>
-      <c r="H202" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I202" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J202" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K202" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L202" s="24" t="s">
-        <v>648</v>
-      </c>
-      <c r="M202" s="24" t="s">
-        <v>649</v>
-      </c>
-      <c r="N202" s="24" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A203">
-        <v>20064</v>
-      </c>
-      <c r="B203" t="s">
-        <v>380</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D203" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E203" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F203" t="s">
-        <v>454</v>
-      </c>
-      <c r="G203" t="s">
-        <v>454</v>
-      </c>
-      <c r="H203" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I203" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J203" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K203" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L203" s="24" t="s">
-        <v>651</v>
-      </c>
-      <c r="M203" s="24" t="s">
-        <v>652</v>
-      </c>
-      <c r="N203" s="24" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A204">
-        <v>20065</v>
-      </c>
-      <c r="B204" t="s">
-        <v>381</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D204" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E204" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F204" t="s">
-        <v>455</v>
-      </c>
-      <c r="G204" t="s">
-        <v>455</v>
-      </c>
-      <c r="H204" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I204" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J204" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K204" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L204" s="24" t="s">
-        <v>654</v>
-      </c>
-      <c r="M204" s="24" t="s">
-        <v>655</v>
-      </c>
-      <c r="N204" s="24" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A205">
-        <v>20066</v>
-      </c>
-      <c r="B205" t="s">
-        <v>382</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D205" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E205" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F205" t="s">
-        <v>456</v>
-      </c>
-      <c r="G205" t="s">
-        <v>456</v>
-      </c>
-      <c r="H205" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I205" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J205" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K205" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L205" s="24" t="s">
-        <v>657</v>
-      </c>
-      <c r="M205" s="24" t="s">
-        <v>658</v>
-      </c>
-      <c r="N205" s="24" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A206">
-        <v>20067</v>
-      </c>
-      <c r="B206" t="s">
-        <v>383</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D206" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E206" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F206" t="s">
-        <v>457</v>
-      </c>
-      <c r="G206" t="s">
-        <v>457</v>
-      </c>
-      <c r="H206" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I206" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J206" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K206" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L206" s="24" t="s">
-        <v>660</v>
-      </c>
-      <c r="M206" s="24" t="s">
-        <v>661</v>
-      </c>
-      <c r="N206" s="24" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A207">
-        <v>20068</v>
-      </c>
-      <c r="B207" t="s">
-        <v>384</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D207" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E207" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F207" t="s">
-        <v>458</v>
-      </c>
-      <c r="G207" t="s">
-        <v>458</v>
-      </c>
-      <c r="H207" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I207" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J207" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K207" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L207" s="24" t="s">
-        <v>663</v>
-      </c>
-      <c r="M207" s="24" t="s">
-        <v>664</v>
-      </c>
-      <c r="N207" s="24" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A208">
-        <v>20069</v>
-      </c>
-      <c r="B208" t="s">
-        <v>385</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D208" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E208" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F208" t="s">
-        <v>459</v>
-      </c>
-      <c r="G208" t="s">
-        <v>459</v>
-      </c>
-      <c r="H208" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I208" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J208" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K208" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L208" s="24" t="s">
-        <v>666</v>
-      </c>
-      <c r="M208" s="24" t="s">
-        <v>667</v>
-      </c>
-      <c r="N208" s="24" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A209">
-        <v>20070</v>
-      </c>
-      <c r="B209" t="s">
-        <v>386</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D209" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E209" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F209" t="s">
-        <v>460</v>
-      </c>
-      <c r="G209" t="s">
-        <v>460</v>
-      </c>
-      <c r="H209" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I209" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J209" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K209" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L209" s="24" t="s">
-        <v>669</v>
-      </c>
-      <c r="M209" s="24" t="s">
-        <v>670</v>
-      </c>
-      <c r="N209" s="24" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A210">
-        <v>20071</v>
-      </c>
-      <c r="B210" t="s">
-        <v>387</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D210" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E210" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F210" t="s">
-        <v>461</v>
-      </c>
-      <c r="G210" t="s">
-        <v>461</v>
-      </c>
-      <c r="H210" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I210" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J210" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K210" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L210" s="24" t="s">
-        <v>672</v>
-      </c>
-      <c r="M210" s="24" t="s">
-        <v>673</v>
-      </c>
-      <c r="N210" s="24" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A211">
-        <v>20072</v>
-      </c>
-      <c r="B211" t="s">
-        <v>388</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D211" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E211" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F211" t="s">
-        <v>462</v>
-      </c>
-      <c r="G211" t="s">
-        <v>462</v>
-      </c>
-      <c r="H211" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I211" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J211" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K211" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L211" s="24" t="s">
-        <v>675</v>
-      </c>
-      <c r="M211" s="24" t="s">
-        <v>676</v>
-      </c>
-      <c r="N211" s="24" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A212">
-        <v>20073</v>
-      </c>
-      <c r="B212" t="s">
-        <v>389</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D212" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E212" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F212" t="s">
-        <v>463</v>
-      </c>
-      <c r="G212" t="s">
-        <v>463</v>
-      </c>
-      <c r="H212" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I212" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J212" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K212" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L212" s="24" t="s">
-        <v>678</v>
-      </c>
-      <c r="M212" s="24" t="s">
-        <v>679</v>
-      </c>
-      <c r="N212" s="24" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="A213">
-        <v>20074</v>
-      </c>
-      <c r="B213" t="s">
-        <v>390</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D213" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E213" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F213" t="s">
-        <v>464</v>
-      </c>
-      <c r="G213" t="s">
-        <v>464</v>
-      </c>
-      <c r="H213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L213" s="24" t="s">
-        <v>681</v>
-      </c>
-      <c r="M213" s="24" t="s">
-        <v>682</v>
-      </c>
-      <c r="N213" s="24" t="s">
-        <v>683</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A4:A102" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\迷宫装备\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CAE7DA-D210-4384-A06A-668354CA216B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E8D2DE-B76E-416D-AB6E-F83FC7BEAE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="685">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1065,6 +1065,1111 @@
   </si>
   <si>
     <t>4:10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击——攻击固定值和</t>
+  </si>
+  <si>
+    <t>攻击——攻击提高和，万分比</t>
+  </si>
+  <si>
+    <t>防御——防御固定值</t>
+  </si>
+  <si>
+    <t>防御——防御提高和，万分比</t>
+  </si>
+  <si>
+    <t>攻击伤害——伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>受到伤害——目标受到伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>额外伤害——额外伤害固定值和</t>
+  </si>
+  <si>
+    <t>受到额外伤害——目标额外受伤固定值和</t>
+  </si>
+  <si>
+    <t>伤害总加成——伤害总加成，万分比</t>
+  </si>
+  <si>
+    <t>受到伤害总加成——目标受伤总加成，万分比</t>
+  </si>
+  <si>
+    <t>攻击速度——攻击速度</t>
+  </si>
+  <si>
+    <t>攻击范围——攻击距离，万分比</t>
+  </si>
+  <si>
+    <t>击中怪物回血——击中怪物回血</t>
+  </si>
+  <si>
+    <t>击中回血效果——击中回血效果提高%</t>
+  </si>
+  <si>
+    <t>暴击几率——暴击几率和，万分比</t>
+  </si>
+  <si>
+    <t>暴击伤害——暴击伤害和，万分比</t>
+  </si>
+  <si>
+    <t>移动速度——移动速度，万分比</t>
+  </si>
+  <si>
+    <t>攻击数量——攻击目标的个数</t>
+  </si>
+  <si>
+    <t>持续伤害提高——无元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高——受到无元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>额外持续伤害——额外无元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>受到额外持续伤害——受到额外无元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>攻击附加冰元素——标记属性，有这个id表示攻击要额外计算冰属性公式</t>
+  </si>
+  <si>
+    <t>攻击附加冰元素系数——冰元素的转换系数，实现方式为：攻击附带额外冰元素攻击，附带的冰攻=角色攻击*冰元素系数</t>
+  </si>
+  <si>
+    <t>冰元素攻击——冰攻击固定值和</t>
+  </si>
+  <si>
+    <t>冰元素攻击——冰攻击提高和，万分比</t>
+  </si>
+  <si>
+    <t>冰元素伤害——冰伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>受到冰元素伤害——目标受到冰伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>额外冰伤害——额外冰伤害固定值和</t>
+  </si>
+  <si>
+    <t>受到额外冰伤害——目标额外受冰伤害固定值和</t>
+  </si>
+  <si>
+    <t>冰持续伤害提高——冰元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>受到冰持续伤害提高——受到冰元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>额外冰持续伤害固定值——额外冰元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>受到额外冰持续伤害固定值——受到额外冰元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>攻击附加火元素——标记属性，有这个id表示攻击要额外计算火属性公式</t>
+  </si>
+  <si>
+    <t>攻击附加火元素系数——火元素的转换系数，实现方式为：攻击附带额外火元素攻击，附带的火攻=角色攻击*火元素系数</t>
+  </si>
+  <si>
+    <t>火元素攻击——火攻击固定值和</t>
+  </si>
+  <si>
+    <t>火元素攻击——火攻击提高和，万分比</t>
+  </si>
+  <si>
+    <t>火元素伤害——火伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>受到火元素伤害——目标受到火伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>额外火伤害——额外火伤害固定值和</t>
+  </si>
+  <si>
+    <t>受到额外火伤害——目标额外受火伤害固定值和</t>
+  </si>
+  <si>
+    <t>火持续伤害提高——火元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>受到火持续伤害提高——受到火元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>额外火持续伤害固定值——额外火元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>受到额外火持续伤害固定值——受到额外火元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>攻击附加电元素——标记属性，有这个id表示攻击要额外计算电属性公式</t>
+  </si>
+  <si>
+    <t>攻击附加电元素系数——电元素的转换系数，实现方式为：攻击附带额外电元素攻击，附带的电攻=角色攻击*电元素系数</t>
+  </si>
+  <si>
+    <t>电元素攻击——电攻击固定值和</t>
+  </si>
+  <si>
+    <t>电元素攻击——电攻击提高和，万分比</t>
+  </si>
+  <si>
+    <t>电元素伤害——电伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>受到电元素伤害——目标受到电伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>额外电伤害——额外电伤害固定值和</t>
+  </si>
+  <si>
+    <t>受到额外电伤害——目标额外受电伤害固定值和</t>
+  </si>
+  <si>
+    <t>电持续伤害提高——电元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>受到电持续伤害提高——受到电元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>额外电持续伤害固定值——额外电元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>受到额外电持续伤害固定值——受到额外电元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>攻击附加毒元素——标记属性，有这个id表示攻击要额外计算毒属性公式</t>
+  </si>
+  <si>
+    <t>攻击附加毒元素系数——毒元素的转换系数，实现方式为：攻击附带额外毒元素攻击，附带的毒攻=角色攻击*毒元素系数</t>
+  </si>
+  <si>
+    <t>毒元素攻击——毒攻击固定值和</t>
+  </si>
+  <si>
+    <t>毒元素攻击——毒攻击提高和，万分比</t>
+  </si>
+  <si>
+    <t>毒元素伤害——毒伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>受到毒元素伤害——目标受到毒伤害提高和，万分比</t>
+  </si>
+  <si>
+    <t>额外毒伤害——额外毒伤害固定值和</t>
+  </si>
+  <si>
+    <t>受到额外毒伤害——目标额外受毒伤害固定值和</t>
+  </si>
+  <si>
+    <t>毒持续伤害提高——毒元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>受到毒持续伤害提高——受到毒元素持续伤害提高，万分比</t>
+  </si>
+  <si>
+    <t>额外毒持续伤害固定值——额外毒元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>受到额外毒持续伤害固定值——受到额外毒元素持续伤害，固定值</t>
+  </si>
+  <si>
+    <t>防御——防御提高%</t>
+  </si>
+  <si>
+    <t>防御——防御提高</t>
+  </si>
+  <si>
+    <t>生命上限——生命值上限提高%</t>
+  </si>
+  <si>
+    <t>生命上限——生命值上限提高</t>
+  </si>
+  <si>
+    <t>20001:1</t>
+  </si>
+  <si>
+    <t>20002:1</t>
+  </si>
+  <si>
+    <t>20003:1</t>
+  </si>
+  <si>
+    <t>20004:1</t>
+  </si>
+  <si>
+    <t>20005:1</t>
+  </si>
+  <si>
+    <t>20006:1</t>
+  </si>
+  <si>
+    <t>20007:1</t>
+  </si>
+  <si>
+    <t>20008:1</t>
+  </si>
+  <si>
+    <t>20009:1</t>
+  </si>
+  <si>
+    <t>20010:1</t>
+  </si>
+  <si>
+    <t>20011:1</t>
+  </si>
+  <si>
+    <t>20012:1</t>
+  </si>
+  <si>
+    <t>20013:1</t>
+  </si>
+  <si>
+    <t>20014:1</t>
+  </si>
+  <si>
+    <t>20015:1</t>
+  </si>
+  <si>
+    <t>20016:1</t>
+  </si>
+  <si>
+    <t>20017:1</t>
+  </si>
+  <si>
+    <t>20018:1</t>
+  </si>
+  <si>
+    <t>20019:1</t>
+  </si>
+  <si>
+    <t>20020:1</t>
+  </si>
+  <si>
+    <t>20021:1</t>
+  </si>
+  <si>
+    <t>20022:1</t>
+  </si>
+  <si>
+    <t>20023:1</t>
+  </si>
+  <si>
+    <t>20024:1</t>
+  </si>
+  <si>
+    <t>20025:1</t>
+  </si>
+  <si>
+    <t>20026:1</t>
+  </si>
+  <si>
+    <t>20027:1</t>
+  </si>
+  <si>
+    <t>20028:1</t>
+  </si>
+  <si>
+    <t>20029:1</t>
+  </si>
+  <si>
+    <t>20030:1</t>
+  </si>
+  <si>
+    <t>20031:1</t>
+  </si>
+  <si>
+    <t>20032:1</t>
+  </si>
+  <si>
+    <t>20033:1</t>
+  </si>
+  <si>
+    <t>20034:1</t>
+  </si>
+  <si>
+    <t>20035:1</t>
+  </si>
+  <si>
+    <t>20036:1</t>
+  </si>
+  <si>
+    <t>20037:1</t>
+  </si>
+  <si>
+    <t>20038:1</t>
+  </si>
+  <si>
+    <t>20039:1</t>
+  </si>
+  <si>
+    <t>20040:1</t>
+  </si>
+  <si>
+    <t>20041:1</t>
+  </si>
+  <si>
+    <t>20042:1</t>
+  </si>
+  <si>
+    <t>20043:1</t>
+  </si>
+  <si>
+    <t>20044:1</t>
+  </si>
+  <si>
+    <t>20045:1</t>
+  </si>
+  <si>
+    <t>20046:1</t>
+  </si>
+  <si>
+    <t>20047:1</t>
+  </si>
+  <si>
+    <t>20048:1</t>
+  </si>
+  <si>
+    <t>20049:1</t>
+  </si>
+  <si>
+    <t>20050:1</t>
+  </si>
+  <si>
+    <t>20051:1</t>
+  </si>
+  <si>
+    <t>20052:1</t>
+  </si>
+  <si>
+    <t>20053:1</t>
+  </si>
+  <si>
+    <t>20054:1</t>
+  </si>
+  <si>
+    <t>20055:1</t>
+  </si>
+  <si>
+    <t>20056:1</t>
+  </si>
+  <si>
+    <t>20057:1</t>
+  </si>
+  <si>
+    <t>20058:1</t>
+  </si>
+  <si>
+    <t>20059:1</t>
+  </si>
+  <si>
+    <t>20060:1</t>
+  </si>
+  <si>
+    <t>20061:1</t>
+  </si>
+  <si>
+    <t>20062:1</t>
+  </si>
+  <si>
+    <t>20063:1</t>
+  </si>
+  <si>
+    <t>20064:1</t>
+  </si>
+  <si>
+    <t>20065:1</t>
+  </si>
+  <si>
+    <t>20066:1</t>
+  </si>
+  <si>
+    <t>20067:1</t>
+  </si>
+  <si>
+    <t>20068:1</t>
+  </si>
+  <si>
+    <t>20069:1</t>
+  </si>
+  <si>
+    <t>20070:1</t>
+  </si>
+  <si>
+    <t>20071:1</t>
+  </si>
+  <si>
+    <t>20072:1</t>
+  </si>
+  <si>
+    <t>20073:1</t>
+  </si>
+  <si>
+    <t>20074:1</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:11</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:11</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:3</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:12</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:12</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:4</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:13</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:13</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:5</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:14</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:14</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:6</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:15</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:15</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:7</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:16</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:16</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:8</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:17</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:17</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:9</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:18</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:18</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:10</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:19</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:19</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:11</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:20</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:20</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:12</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:21</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:21</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:13</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:22</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:22</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:14</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:23</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:23</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:15</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:24</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:24</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:16</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:25</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:25</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:17</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:26</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:26</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:18</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:27</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:27</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:19</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:28</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:28</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:20</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:29</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:29</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:21</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:30</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:30</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:22</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:31</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:31</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:23</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:32</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:32</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:24</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:33</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:33</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:25</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:34</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:34</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:26</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:35</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:35</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:27</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:36</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:36</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:28</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:37</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:37</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:29</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:38</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:38</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:30</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:39</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:39</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:31</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:40</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:40</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:32</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:41</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:41</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:33</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:42</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:42</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:34</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:43</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:43</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:35</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:44</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:44</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:36</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:45</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:45</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:37</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:46</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:46</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:38</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:47</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:47</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:39</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:48</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:48</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:40</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:49</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:49</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:41</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:50</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:50</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:42</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:51</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:51</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:43</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:52</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:52</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:44</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:53</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:53</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:45</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:54</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:54</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:46</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:55</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:55</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:47</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:56</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:56</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:48</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:57</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:57</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:49</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:58</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:58</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:50</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:59</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:59</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:51</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:60</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:60</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:52</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:61</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:61</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:53</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:62</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:62</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:54</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:63</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:63</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:55</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:64</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:64</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:56</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:65</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:65</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:57</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:66</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:66</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:58</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:67</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:67</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:59</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:68</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:68</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:60</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:69</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:69</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:61</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:70</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:70</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:62</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:71</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:71</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:63</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:72</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:72</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:64</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:73</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:73</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:65</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:74</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:74</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:66</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:75</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:75</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:67</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:76</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:76</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:68</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:77</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:77</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:69</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:78</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:78</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:70</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:79</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:79</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:71</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:80</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:80</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:72</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:81</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:81</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:73</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:82</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:82</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:74</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:83</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:83</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:75</t>
+  </si>
+  <si>
+    <t>1001112:1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1546,7 +2651,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -7642,6 +8747,3262 @@
         <v>314</v>
       </c>
     </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A140">
+        <v>20001</v>
+      </c>
+      <c r="B140" t="s">
+        <v>317</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E140" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="G140" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K140" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L140" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="M140" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="N140" s="24" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A141">
+        <v>20002</v>
+      </c>
+      <c r="B141" t="s">
+        <v>318</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F141" t="s">
+        <v>392</v>
+      </c>
+      <c r="G141" t="s">
+        <v>392</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J141" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K141" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L141" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="M141" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="N141" s="24" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A142">
+        <v>20003</v>
+      </c>
+      <c r="B142" t="s">
+        <v>319</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E142" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F142" t="s">
+        <v>393</v>
+      </c>
+      <c r="G142" t="s">
+        <v>393</v>
+      </c>
+      <c r="H142" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K142" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L142" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="M142" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="N142" s="24" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A143">
+        <v>20004</v>
+      </c>
+      <c r="B143" t="s">
+        <v>320</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E143" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F143" t="s">
+        <v>394</v>
+      </c>
+      <c r="G143" t="s">
+        <v>394</v>
+      </c>
+      <c r="H143" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K143" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L143" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="M143" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="N143" s="24" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A144">
+        <v>20005</v>
+      </c>
+      <c r="B144" t="s">
+        <v>321</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E144" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F144" t="s">
+        <v>395</v>
+      </c>
+      <c r="G144" t="s">
+        <v>395</v>
+      </c>
+      <c r="H144" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K144" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L144" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="M144" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="N144" s="24" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A145">
+        <v>20006</v>
+      </c>
+      <c r="B145" t="s">
+        <v>322</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E145" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F145" t="s">
+        <v>396</v>
+      </c>
+      <c r="G145" t="s">
+        <v>396</v>
+      </c>
+      <c r="H145" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J145" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K145" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L145" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="M145" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="N145" s="24" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A146">
+        <v>20007</v>
+      </c>
+      <c r="B146" t="s">
+        <v>323</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F146" t="s">
+        <v>397</v>
+      </c>
+      <c r="G146" t="s">
+        <v>397</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K146" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L146" s="24" t="s">
+        <v>480</v>
+      </c>
+      <c r="M146" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="N146" s="24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A147">
+        <v>20008</v>
+      </c>
+      <c r="B147" t="s">
+        <v>324</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F147" t="s">
+        <v>398</v>
+      </c>
+      <c r="G147" t="s">
+        <v>398</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J147" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K147" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L147" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="M147" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="N147" s="24" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A148">
+        <v>20009</v>
+      </c>
+      <c r="B148" t="s">
+        <v>325</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E148" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F148" t="s">
+        <v>399</v>
+      </c>
+      <c r="G148" t="s">
+        <v>399</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K148" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L148" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="M148" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="N148" s="24" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A149">
+        <v>20010</v>
+      </c>
+      <c r="B149" t="s">
+        <v>326</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E149" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F149" t="s">
+        <v>400</v>
+      </c>
+      <c r="G149" t="s">
+        <v>400</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K149" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L149" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="M149" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="N149" s="24" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A150">
+        <v>20011</v>
+      </c>
+      <c r="B150" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E150" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F150" t="s">
+        <v>401</v>
+      </c>
+      <c r="G150" t="s">
+        <v>401</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K150" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L150" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="M150" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="N150" s="24" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A151">
+        <v>20012</v>
+      </c>
+      <c r="B151" t="s">
+        <v>328</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F151" t="s">
+        <v>402</v>
+      </c>
+      <c r="G151" t="s">
+        <v>402</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J151" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K151" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L151" s="24" t="s">
+        <v>495</v>
+      </c>
+      <c r="M151" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="N151" s="24" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A152">
+        <v>20013</v>
+      </c>
+      <c r="B152" t="s">
+        <v>329</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F152" t="s">
+        <v>403</v>
+      </c>
+      <c r="G152" t="s">
+        <v>403</v>
+      </c>
+      <c r="H152" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I152" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K152" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L152" s="24" t="s">
+        <v>498</v>
+      </c>
+      <c r="M152" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="N152" s="24" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A153">
+        <v>20014</v>
+      </c>
+      <c r="B153" t="s">
+        <v>330</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E153" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F153" t="s">
+        <v>404</v>
+      </c>
+      <c r="G153" t="s">
+        <v>404</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I153" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K153" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L153" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="M153" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="N153" s="24" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A154">
+        <v>20015</v>
+      </c>
+      <c r="B154" t="s">
+        <v>331</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E154" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F154" t="s">
+        <v>405</v>
+      </c>
+      <c r="G154" t="s">
+        <v>405</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I154" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L154" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="M154" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="N154" s="24" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A155">
+        <v>20016</v>
+      </c>
+      <c r="B155" t="s">
+        <v>332</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E155" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F155" t="s">
+        <v>406</v>
+      </c>
+      <c r="G155" t="s">
+        <v>406</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L155" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="M155" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="N155" s="24" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A156">
+        <v>20017</v>
+      </c>
+      <c r="B156" t="s">
+        <v>333</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E156" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F156" t="s">
+        <v>407</v>
+      </c>
+      <c r="G156" t="s">
+        <v>407</v>
+      </c>
+      <c r="H156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L156" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="M156" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="N156" s="24" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A157">
+        <v>20018</v>
+      </c>
+      <c r="B157" t="s">
+        <v>334</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E157" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F157" t="s">
+        <v>408</v>
+      </c>
+      <c r="G157" t="s">
+        <v>408</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L157" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="M157" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="N157" s="24" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A158">
+        <v>20019</v>
+      </c>
+      <c r="B158" t="s">
+        <v>335</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E158" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F158" t="s">
+        <v>409</v>
+      </c>
+      <c r="G158" t="s">
+        <v>409</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K158" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L158" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="M158" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="N158" s="24" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A159">
+        <v>20020</v>
+      </c>
+      <c r="B159" t="s">
+        <v>336</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E159" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F159" t="s">
+        <v>410</v>
+      </c>
+      <c r="G159" t="s">
+        <v>410</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K159" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L159" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="M159" s="24" t="s">
+        <v>520</v>
+      </c>
+      <c r="N159" s="24" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A160">
+        <v>20021</v>
+      </c>
+      <c r="B160" t="s">
+        <v>337</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E160" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F160" t="s">
+        <v>411</v>
+      </c>
+      <c r="G160" t="s">
+        <v>411</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K160" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L160" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="M160" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="N160" s="24" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A161">
+        <v>20022</v>
+      </c>
+      <c r="B161" t="s">
+        <v>338</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F161" t="s">
+        <v>412</v>
+      </c>
+      <c r="G161" t="s">
+        <v>412</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K161" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L161" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="M161" s="24" t="s">
+        <v>526</v>
+      </c>
+      <c r="N161" s="24" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A162">
+        <v>20023</v>
+      </c>
+      <c r="B162" t="s">
+        <v>339</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E162" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F162" t="s">
+        <v>413</v>
+      </c>
+      <c r="G162" t="s">
+        <v>413</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K162" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L162" s="24" t="s">
+        <v>528</v>
+      </c>
+      <c r="M162" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="N162" s="24" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A163">
+        <v>20024</v>
+      </c>
+      <c r="B163" t="s">
+        <v>340</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F163" t="s">
+        <v>414</v>
+      </c>
+      <c r="G163" t="s">
+        <v>414</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K163" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L163" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="M163" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="N163" s="24" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A164">
+        <v>20025</v>
+      </c>
+      <c r="B164" t="s">
+        <v>341</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E164" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F164" t="s">
+        <v>415</v>
+      </c>
+      <c r="G164" t="s">
+        <v>415</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K164" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L164" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="M164" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="N164" s="24" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A165">
+        <v>20026</v>
+      </c>
+      <c r="B165" t="s">
+        <v>342</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E165" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F165" t="s">
+        <v>416</v>
+      </c>
+      <c r="G165" t="s">
+        <v>416</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I165" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J165" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K165" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L165" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="M165" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="N165" s="24" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A166">
+        <v>20027</v>
+      </c>
+      <c r="B166" t="s">
+        <v>343</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E166" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F166" t="s">
+        <v>417</v>
+      </c>
+      <c r="G166" t="s">
+        <v>417</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K166" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L166" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="M166" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="N166" s="24" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A167">
+        <v>20028</v>
+      </c>
+      <c r="B167" t="s">
+        <v>344</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E167" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F167" t="s">
+        <v>418</v>
+      </c>
+      <c r="G167" t="s">
+        <v>418</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K167" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L167" s="24" t="s">
+        <v>543</v>
+      </c>
+      <c r="M167" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="N167" s="24" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A168">
+        <v>20029</v>
+      </c>
+      <c r="B168" t="s">
+        <v>345</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F168" t="s">
+        <v>419</v>
+      </c>
+      <c r="G168" t="s">
+        <v>419</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I168" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K168" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L168" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="M168" s="24" t="s">
+        <v>547</v>
+      </c>
+      <c r="N168" s="24" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A169">
+        <v>20030</v>
+      </c>
+      <c r="B169" t="s">
+        <v>346</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E169" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F169" t="s">
+        <v>420</v>
+      </c>
+      <c r="G169" t="s">
+        <v>420</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K169" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L169" s="24" t="s">
+        <v>549</v>
+      </c>
+      <c r="M169" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="N169" s="24" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A170">
+        <v>20031</v>
+      </c>
+      <c r="B170" t="s">
+        <v>347</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E170" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F170" t="s">
+        <v>421</v>
+      </c>
+      <c r="G170" t="s">
+        <v>421</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K170" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L170" s="24" t="s">
+        <v>552</v>
+      </c>
+      <c r="M170" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="N170" s="24" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A171">
+        <v>20032</v>
+      </c>
+      <c r="B171" t="s">
+        <v>348</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F171" t="s">
+        <v>422</v>
+      </c>
+      <c r="G171" t="s">
+        <v>422</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K171" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L171" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="M171" s="24" t="s">
+        <v>556</v>
+      </c>
+      <c r="N171" s="24" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A172">
+        <v>20033</v>
+      </c>
+      <c r="B172" t="s">
+        <v>349</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E172" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F172" t="s">
+        <v>423</v>
+      </c>
+      <c r="G172" t="s">
+        <v>423</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L172" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="M172" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="N172" s="24" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A173">
+        <v>20034</v>
+      </c>
+      <c r="B173" t="s">
+        <v>350</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E173" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F173" t="s">
+        <v>424</v>
+      </c>
+      <c r="G173" t="s">
+        <v>424</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K173" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L173" s="24" t="s">
+        <v>561</v>
+      </c>
+      <c r="M173" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="N173" s="24" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A174">
+        <v>20035</v>
+      </c>
+      <c r="B174" t="s">
+        <v>351</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E174" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F174" t="s">
+        <v>425</v>
+      </c>
+      <c r="G174" t="s">
+        <v>425</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J174" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K174" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L174" s="24" t="s">
+        <v>564</v>
+      </c>
+      <c r="M174" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="N174" s="24" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A175">
+        <v>20036</v>
+      </c>
+      <c r="B175" t="s">
+        <v>352</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E175" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F175" t="s">
+        <v>426</v>
+      </c>
+      <c r="G175" t="s">
+        <v>426</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J175" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K175" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L175" s="24" t="s">
+        <v>567</v>
+      </c>
+      <c r="M175" s="24" t="s">
+        <v>568</v>
+      </c>
+      <c r="N175" s="24" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A176">
+        <v>20037</v>
+      </c>
+      <c r="B176" t="s">
+        <v>353</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E176" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F176" t="s">
+        <v>427</v>
+      </c>
+      <c r="G176" t="s">
+        <v>427</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L176" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="M176" s="24" t="s">
+        <v>571</v>
+      </c>
+      <c r="N176" s="24" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A177">
+        <v>20038</v>
+      </c>
+      <c r="B177" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E177" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F177" t="s">
+        <v>428</v>
+      </c>
+      <c r="G177" t="s">
+        <v>428</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J177" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K177" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L177" s="24" t="s">
+        <v>573</v>
+      </c>
+      <c r="M177" s="24" t="s">
+        <v>574</v>
+      </c>
+      <c r="N177" s="24" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A178">
+        <v>20039</v>
+      </c>
+      <c r="B178" t="s">
+        <v>355</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E178" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F178" t="s">
+        <v>429</v>
+      </c>
+      <c r="G178" t="s">
+        <v>429</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L178" s="24" t="s">
+        <v>576</v>
+      </c>
+      <c r="M178" s="24" t="s">
+        <v>577</v>
+      </c>
+      <c r="N178" s="24" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A179">
+        <v>20040</v>
+      </c>
+      <c r="B179" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E179" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F179" t="s">
+        <v>430</v>
+      </c>
+      <c r="G179" t="s">
+        <v>430</v>
+      </c>
+      <c r="H179" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K179" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L179" s="24" t="s">
+        <v>579</v>
+      </c>
+      <c r="M179" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="N179" s="24" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A180">
+        <v>20041</v>
+      </c>
+      <c r="B180" t="s">
+        <v>357</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E180" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F180" t="s">
+        <v>431</v>
+      </c>
+      <c r="G180" t="s">
+        <v>431</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K180" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L180" s="24" t="s">
+        <v>582</v>
+      </c>
+      <c r="M180" s="24" t="s">
+        <v>583</v>
+      </c>
+      <c r="N180" s="24" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A181">
+        <v>20042</v>
+      </c>
+      <c r="B181" t="s">
+        <v>358</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E181" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F181" t="s">
+        <v>432</v>
+      </c>
+      <c r="G181" t="s">
+        <v>432</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K181" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L181" s="24" t="s">
+        <v>585</v>
+      </c>
+      <c r="M181" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="N181" s="24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A182">
+        <v>20043</v>
+      </c>
+      <c r="B182" t="s">
+        <v>359</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E182" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F182" t="s">
+        <v>433</v>
+      </c>
+      <c r="G182" t="s">
+        <v>433</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K182" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L182" s="24" t="s">
+        <v>588</v>
+      </c>
+      <c r="M182" s="24" t="s">
+        <v>589</v>
+      </c>
+      <c r="N182" s="24" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A183">
+        <v>20044</v>
+      </c>
+      <c r="B183" t="s">
+        <v>360</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E183" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F183" t="s">
+        <v>434</v>
+      </c>
+      <c r="G183" t="s">
+        <v>434</v>
+      </c>
+      <c r="H183" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J183" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K183" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L183" s="24" t="s">
+        <v>591</v>
+      </c>
+      <c r="M183" s="24" t="s">
+        <v>592</v>
+      </c>
+      <c r="N183" s="24" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A184">
+        <v>20045</v>
+      </c>
+      <c r="B184" t="s">
+        <v>361</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E184" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F184" t="s">
+        <v>435</v>
+      </c>
+      <c r="G184" t="s">
+        <v>435</v>
+      </c>
+      <c r="H184" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K184" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L184" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="M184" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="N184" s="24" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A185">
+        <v>20046</v>
+      </c>
+      <c r="B185" t="s">
+        <v>362</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E185" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F185" t="s">
+        <v>436</v>
+      </c>
+      <c r="G185" t="s">
+        <v>436</v>
+      </c>
+      <c r="H185" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K185" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L185" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="M185" s="24" t="s">
+        <v>598</v>
+      </c>
+      <c r="N185" s="24" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A186">
+        <v>20047</v>
+      </c>
+      <c r="B186" t="s">
+        <v>363</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E186" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F186" t="s">
+        <v>437</v>
+      </c>
+      <c r="G186" t="s">
+        <v>437</v>
+      </c>
+      <c r="H186" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K186" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L186" s="24" t="s">
+        <v>600</v>
+      </c>
+      <c r="M186" s="24" t="s">
+        <v>601</v>
+      </c>
+      <c r="N186" s="24" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A187">
+        <v>20048</v>
+      </c>
+      <c r="B187" t="s">
+        <v>364</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E187" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F187" t="s">
+        <v>438</v>
+      </c>
+      <c r="G187" t="s">
+        <v>438</v>
+      </c>
+      <c r="H187" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K187" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L187" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="M187" s="24" t="s">
+        <v>604</v>
+      </c>
+      <c r="N187" s="24" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A188">
+        <v>20049</v>
+      </c>
+      <c r="B188" t="s">
+        <v>365</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E188" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F188" t="s">
+        <v>439</v>
+      </c>
+      <c r="G188" t="s">
+        <v>439</v>
+      </c>
+      <c r="H188" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K188" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L188" s="24" t="s">
+        <v>606</v>
+      </c>
+      <c r="M188" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="N188" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A189">
+        <v>20050</v>
+      </c>
+      <c r="B189" t="s">
+        <v>366</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E189" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F189" t="s">
+        <v>440</v>
+      </c>
+      <c r="G189" t="s">
+        <v>440</v>
+      </c>
+      <c r="H189" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J189" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K189" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L189" s="24" t="s">
+        <v>609</v>
+      </c>
+      <c r="M189" s="24" t="s">
+        <v>610</v>
+      </c>
+      <c r="N189" s="24" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A190">
+        <v>20051</v>
+      </c>
+      <c r="B190" t="s">
+        <v>367</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E190" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F190" t="s">
+        <v>441</v>
+      </c>
+      <c r="G190" t="s">
+        <v>441</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K190" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L190" s="24" t="s">
+        <v>612</v>
+      </c>
+      <c r="M190" s="24" t="s">
+        <v>613</v>
+      </c>
+      <c r="N190" s="24" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A191">
+        <v>20052</v>
+      </c>
+      <c r="B191" t="s">
+        <v>368</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E191" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F191" t="s">
+        <v>442</v>
+      </c>
+      <c r="G191" t="s">
+        <v>442</v>
+      </c>
+      <c r="H191" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J191" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K191" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L191" s="24" t="s">
+        <v>615</v>
+      </c>
+      <c r="M191" s="24" t="s">
+        <v>616</v>
+      </c>
+      <c r="N191" s="24" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A192">
+        <v>20053</v>
+      </c>
+      <c r="B192" t="s">
+        <v>369</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E192" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F192" t="s">
+        <v>443</v>
+      </c>
+      <c r="G192" t="s">
+        <v>443</v>
+      </c>
+      <c r="H192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L192" s="24" t="s">
+        <v>618</v>
+      </c>
+      <c r="M192" s="24" t="s">
+        <v>619</v>
+      </c>
+      <c r="N192" s="24" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A193">
+        <v>20054</v>
+      </c>
+      <c r="B193" t="s">
+        <v>370</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E193" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F193" t="s">
+        <v>444</v>
+      </c>
+      <c r="G193" t="s">
+        <v>444</v>
+      </c>
+      <c r="H193" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J193" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K193" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L193" s="24" t="s">
+        <v>621</v>
+      </c>
+      <c r="M193" s="24" t="s">
+        <v>622</v>
+      </c>
+      <c r="N193" s="24" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A194">
+        <v>20055</v>
+      </c>
+      <c r="B194" t="s">
+        <v>371</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E194" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F194" t="s">
+        <v>445</v>
+      </c>
+      <c r="G194" t="s">
+        <v>445</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K194" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L194" s="24" t="s">
+        <v>624</v>
+      </c>
+      <c r="M194" s="24" t="s">
+        <v>625</v>
+      </c>
+      <c r="N194" s="24" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A195">
+        <v>20056</v>
+      </c>
+      <c r="B195" t="s">
+        <v>372</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E195" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F195" t="s">
+        <v>446</v>
+      </c>
+      <c r="G195" t="s">
+        <v>446</v>
+      </c>
+      <c r="H195" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J195" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K195" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L195" s="24" t="s">
+        <v>627</v>
+      </c>
+      <c r="M195" s="24" t="s">
+        <v>628</v>
+      </c>
+      <c r="N195" s="24" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A196">
+        <v>20057</v>
+      </c>
+      <c r="B196" t="s">
+        <v>373</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E196" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F196" t="s">
+        <v>447</v>
+      </c>
+      <c r="G196" t="s">
+        <v>447</v>
+      </c>
+      <c r="H196" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K196" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L196" s="24" t="s">
+        <v>630</v>
+      </c>
+      <c r="M196" s="24" t="s">
+        <v>631</v>
+      </c>
+      <c r="N196" s="24" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A197">
+        <v>20058</v>
+      </c>
+      <c r="B197" t="s">
+        <v>374</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E197" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F197" t="s">
+        <v>448</v>
+      </c>
+      <c r="G197" t="s">
+        <v>448</v>
+      </c>
+      <c r="H197" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K197" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L197" s="24" t="s">
+        <v>633</v>
+      </c>
+      <c r="M197" s="24" t="s">
+        <v>634</v>
+      </c>
+      <c r="N197" s="24" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A198">
+        <v>20059</v>
+      </c>
+      <c r="B198" t="s">
+        <v>375</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E198" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F198" t="s">
+        <v>449</v>
+      </c>
+      <c r="G198" t="s">
+        <v>449</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K198" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L198" s="24" t="s">
+        <v>636</v>
+      </c>
+      <c r="M198" s="24" t="s">
+        <v>637</v>
+      </c>
+      <c r="N198" s="24" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A199">
+        <v>20060</v>
+      </c>
+      <c r="B199" t="s">
+        <v>376</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E199" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F199" t="s">
+        <v>450</v>
+      </c>
+      <c r="G199" t="s">
+        <v>450</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J199" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K199" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L199" s="24" t="s">
+        <v>639</v>
+      </c>
+      <c r="M199" s="24" t="s">
+        <v>640</v>
+      </c>
+      <c r="N199" s="24" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A200">
+        <v>20061</v>
+      </c>
+      <c r="B200" t="s">
+        <v>377</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E200" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F200" t="s">
+        <v>451</v>
+      </c>
+      <c r="G200" t="s">
+        <v>451</v>
+      </c>
+      <c r="H200" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K200" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L200" s="24" t="s">
+        <v>642</v>
+      </c>
+      <c r="M200" s="24" t="s">
+        <v>643</v>
+      </c>
+      <c r="N200" s="24" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A201">
+        <v>20062</v>
+      </c>
+      <c r="B201" t="s">
+        <v>378</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E201" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F201" t="s">
+        <v>452</v>
+      </c>
+      <c r="G201" t="s">
+        <v>452</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J201" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K201" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L201" s="24" t="s">
+        <v>645</v>
+      </c>
+      <c r="M201" s="24" t="s">
+        <v>646</v>
+      </c>
+      <c r="N201" s="24" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A202">
+        <v>20063</v>
+      </c>
+      <c r="B202" t="s">
+        <v>379</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E202" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F202" t="s">
+        <v>453</v>
+      </c>
+      <c r="G202" t="s">
+        <v>453</v>
+      </c>
+      <c r="H202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L202" s="24" t="s">
+        <v>648</v>
+      </c>
+      <c r="M202" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="N202" s="24" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A203">
+        <v>20064</v>
+      </c>
+      <c r="B203" t="s">
+        <v>380</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E203" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F203" t="s">
+        <v>454</v>
+      </c>
+      <c r="G203" t="s">
+        <v>454</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J203" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K203" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L203" s="24" t="s">
+        <v>651</v>
+      </c>
+      <c r="M203" s="24" t="s">
+        <v>652</v>
+      </c>
+      <c r="N203" s="24" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A204">
+        <v>20065</v>
+      </c>
+      <c r="B204" t="s">
+        <v>381</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E204" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F204" t="s">
+        <v>455</v>
+      </c>
+      <c r="G204" t="s">
+        <v>455</v>
+      </c>
+      <c r="H204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L204" s="24" t="s">
+        <v>654</v>
+      </c>
+      <c r="M204" s="24" t="s">
+        <v>655</v>
+      </c>
+      <c r="N204" s="24" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A205">
+        <v>20066</v>
+      </c>
+      <c r="B205" t="s">
+        <v>382</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E205" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F205" t="s">
+        <v>456</v>
+      </c>
+      <c r="G205" t="s">
+        <v>456</v>
+      </c>
+      <c r="H205" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K205" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L205" s="24" t="s">
+        <v>657</v>
+      </c>
+      <c r="M205" s="24" t="s">
+        <v>658</v>
+      </c>
+      <c r="N205" s="24" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A206">
+        <v>20067</v>
+      </c>
+      <c r="B206" t="s">
+        <v>383</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E206" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F206" t="s">
+        <v>457</v>
+      </c>
+      <c r="G206" t="s">
+        <v>457</v>
+      </c>
+      <c r="H206" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K206" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L206" s="24" t="s">
+        <v>660</v>
+      </c>
+      <c r="M206" s="24" t="s">
+        <v>661</v>
+      </c>
+      <c r="N206" s="24" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A207">
+        <v>20068</v>
+      </c>
+      <c r="B207" t="s">
+        <v>384</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E207" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F207" t="s">
+        <v>458</v>
+      </c>
+      <c r="G207" t="s">
+        <v>458</v>
+      </c>
+      <c r="H207" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I207" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K207" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L207" s="24" t="s">
+        <v>663</v>
+      </c>
+      <c r="M207" s="24" t="s">
+        <v>664</v>
+      </c>
+      <c r="N207" s="24" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A208">
+        <v>20069</v>
+      </c>
+      <c r="B208" t="s">
+        <v>385</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E208" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F208" t="s">
+        <v>459</v>
+      </c>
+      <c r="G208" t="s">
+        <v>459</v>
+      </c>
+      <c r="H208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L208" s="24" t="s">
+        <v>666</v>
+      </c>
+      <c r="M208" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="N208" s="24" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A209">
+        <v>20070</v>
+      </c>
+      <c r="B209" t="s">
+        <v>386</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E209" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F209" t="s">
+        <v>460</v>
+      </c>
+      <c r="G209" t="s">
+        <v>460</v>
+      </c>
+      <c r="H209" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K209" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L209" s="24" t="s">
+        <v>669</v>
+      </c>
+      <c r="M209" s="24" t="s">
+        <v>670</v>
+      </c>
+      <c r="N209" s="24" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A210">
+        <v>20071</v>
+      </c>
+      <c r="B210" t="s">
+        <v>387</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E210" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F210" t="s">
+        <v>461</v>
+      </c>
+      <c r="G210" t="s">
+        <v>461</v>
+      </c>
+      <c r="H210" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K210" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L210" s="24" t="s">
+        <v>672</v>
+      </c>
+      <c r="M210" s="24" t="s">
+        <v>673</v>
+      </c>
+      <c r="N210" s="24" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A211">
+        <v>20072</v>
+      </c>
+      <c r="B211" t="s">
+        <v>388</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E211" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F211" t="s">
+        <v>462</v>
+      </c>
+      <c r="G211" t="s">
+        <v>462</v>
+      </c>
+      <c r="H211" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K211" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L211" s="24" t="s">
+        <v>675</v>
+      </c>
+      <c r="M211" s="24" t="s">
+        <v>676</v>
+      </c>
+      <c r="N211" s="24" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A212">
+        <v>20073</v>
+      </c>
+      <c r="B212" t="s">
+        <v>389</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E212" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F212" t="s">
+        <v>463</v>
+      </c>
+      <c r="G212" t="s">
+        <v>463</v>
+      </c>
+      <c r="H212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L212" s="24" t="s">
+        <v>678</v>
+      </c>
+      <c r="M212" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="N212" s="24" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A213">
+        <v>20074</v>
+      </c>
+      <c r="B213" t="s">
+        <v>390</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E213" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F213" t="s">
+        <v>464</v>
+      </c>
+      <c r="G213" t="s">
+        <v>464</v>
+      </c>
+      <c r="H213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L213" s="24" t="s">
+        <v>681</v>
+      </c>
+      <c r="M213" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="N213" s="24" t="s">
+        <v>683</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:A102" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_equip_affix_sp_rule_v8【迷宫-装备-生成特殊词条规则】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E8D2DE-B76E-416D-AB6E-F83FC7BEAE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C175B821-E5B5-40CC-957F-D7428589A153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2764" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2803" uniqueCount="692">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1290,886 +1290,917 @@
     <t>生命上限——生命值上限提高</t>
   </si>
   <si>
+    <t>20004:1</t>
+  </si>
+  <si>
+    <t>20005:1</t>
+  </si>
+  <si>
+    <t>20006:1</t>
+  </si>
+  <si>
+    <t>20007:1</t>
+  </si>
+  <si>
+    <t>20008:1</t>
+  </si>
+  <si>
+    <t>20009:1</t>
+  </si>
+  <si>
+    <t>20010:1</t>
+  </si>
+  <si>
+    <t>20011:1</t>
+  </si>
+  <si>
+    <t>20012:1</t>
+  </si>
+  <si>
+    <t>20013:1</t>
+  </si>
+  <si>
+    <t>20014:1</t>
+  </si>
+  <si>
+    <t>20015:1</t>
+  </si>
+  <si>
+    <t>20016:1</t>
+  </si>
+  <si>
+    <t>20017:1</t>
+  </si>
+  <si>
+    <t>20018:1</t>
+  </si>
+  <si>
+    <t>20019:1</t>
+  </si>
+  <si>
+    <t>20020:1</t>
+  </si>
+  <si>
+    <t>20021:1</t>
+  </si>
+  <si>
+    <t>20022:1</t>
+  </si>
+  <si>
+    <t>20023:1</t>
+  </si>
+  <si>
+    <t>20024:1</t>
+  </si>
+  <si>
+    <t>20025:1</t>
+  </si>
+  <si>
+    <t>20026:1</t>
+  </si>
+  <si>
+    <t>20027:1</t>
+  </si>
+  <si>
+    <t>20028:1</t>
+  </si>
+  <si>
+    <t>20029:1</t>
+  </si>
+  <si>
+    <t>20030:1</t>
+  </si>
+  <si>
+    <t>20031:1</t>
+  </si>
+  <si>
+    <t>20032:1</t>
+  </si>
+  <si>
+    <t>20033:1</t>
+  </si>
+  <si>
+    <t>20034:1</t>
+  </si>
+  <si>
+    <t>20035:1</t>
+  </si>
+  <si>
+    <t>20036:1</t>
+  </si>
+  <si>
+    <t>20037:1</t>
+  </si>
+  <si>
+    <t>20038:1</t>
+  </si>
+  <si>
+    <t>20039:1</t>
+  </si>
+  <si>
+    <t>20040:1</t>
+  </si>
+  <si>
+    <t>20041:1</t>
+  </si>
+  <si>
+    <t>20042:1</t>
+  </si>
+  <si>
+    <t>20043:1</t>
+  </si>
+  <si>
+    <t>20044:1</t>
+  </si>
+  <si>
+    <t>20045:1</t>
+  </si>
+  <si>
+    <t>20046:1</t>
+  </si>
+  <si>
+    <t>20047:1</t>
+  </si>
+  <si>
+    <t>20048:1</t>
+  </si>
+  <si>
+    <t>20049:1</t>
+  </si>
+  <si>
+    <t>20050:1</t>
+  </si>
+  <si>
+    <t>20051:1</t>
+  </si>
+  <si>
+    <t>20052:1</t>
+  </si>
+  <si>
+    <t>20053:1</t>
+  </si>
+  <si>
+    <t>20054:1</t>
+  </si>
+  <si>
+    <t>20055:1</t>
+  </si>
+  <si>
+    <t>20056:1</t>
+  </si>
+  <si>
+    <t>20057:1</t>
+  </si>
+  <si>
+    <t>20058:1</t>
+  </si>
+  <si>
+    <t>20059:1</t>
+  </si>
+  <si>
+    <t>20060:1</t>
+  </si>
+  <si>
+    <t>20061:1</t>
+  </si>
+  <si>
+    <t>20062:1</t>
+  </si>
+  <si>
+    <t>20063:1</t>
+  </si>
+  <si>
+    <t>20064:1</t>
+  </si>
+  <si>
+    <t>20065:1</t>
+  </si>
+  <si>
+    <t>20066:1</t>
+  </si>
+  <si>
+    <t>20067:1</t>
+  </si>
+  <si>
+    <t>20068:1</t>
+  </si>
+  <si>
+    <t>20069:1</t>
+  </si>
+  <si>
+    <t>20070:1</t>
+  </si>
+  <si>
+    <t>20071:1</t>
+  </si>
+  <si>
+    <t>20072:1</t>
+  </si>
+  <si>
+    <t>20073:1</t>
+  </si>
+  <si>
+    <t>20074:1</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:11</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:11</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:3</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:12</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:12</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:4</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:13</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:13</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:5</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:14</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:14</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:6</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:15</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:15</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:7</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:16</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:16</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:8</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:17</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:17</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:9</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:18</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:18</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:10</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:19</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:19</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:11</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:20</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:20</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:12</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:21</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:21</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:13</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:22</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:22</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:14</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:23</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:23</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:15</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:24</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:24</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:16</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:25</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:25</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:17</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:26</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:26</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:18</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:27</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:27</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:19</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:28</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:28</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:20</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:29</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:29</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:21</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:30</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:30</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:22</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:31</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:31</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:23</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:32</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:32</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:24</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:33</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:33</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:25</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:34</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:34</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:26</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:35</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:35</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:27</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:36</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:36</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:28</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:37</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:37</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:29</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:38</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:38</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:30</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:39</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:39</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:31</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:40</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:40</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:32</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:41</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:41</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:33</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:42</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:42</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:34</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:43</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:43</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:35</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:44</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:44</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:36</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:45</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:45</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:37</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:46</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:46</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:38</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:47</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:47</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:39</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:48</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:48</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:40</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:49</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:49</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:41</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:50</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:50</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:42</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:51</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:51</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:43</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:52</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:52</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:44</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:53</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:53</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:45</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:54</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:54</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:46</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:55</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:55</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:47</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:56</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:56</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:48</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:57</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:57</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:49</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:58</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:58</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:50</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:59</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:59</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:51</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:60</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:60</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:52</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:61</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:61</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:53</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:62</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:62</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:54</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:63</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:63</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:55</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:64</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:64</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:56</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:65</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:65</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:57</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:66</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:66</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:58</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:67</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:67</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:59</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:68</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:68</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:60</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:69</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:69</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:61</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:70</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:70</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:62</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:71</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:71</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:63</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:72</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:72</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:64</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:73</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:73</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:65</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:74</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:74</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:66</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:75</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:75</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:67</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:76</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:76</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:68</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:77</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:77</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:69</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:78</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:78</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:70</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:79</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:79</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:71</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:80</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:80</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:72</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:81</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:81</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:73</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:82</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:82</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:74</t>
+  </si>
+  <si>
+    <t>0:100_1:10_2:10_3:10_4:10_5:83</t>
+  </si>
+  <si>
+    <t>1:10_2:10_3:10_4:10_5:83</t>
+  </si>
+  <si>
+    <t>1001811:1_3001811:75</t>
+  </si>
+  <si>
+    <t>1001112:1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10319:100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10320:100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10321:100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器，冰弹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器，陨石</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器，雷电</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>20001:1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>20002:1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>20003:1</t>
-  </si>
-  <si>
-    <t>20004:1</t>
-  </si>
-  <si>
-    <t>20005:1</t>
-  </si>
-  <si>
-    <t>20006:1</t>
-  </si>
-  <si>
-    <t>20007:1</t>
-  </si>
-  <si>
-    <t>20008:1</t>
-  </si>
-  <si>
-    <t>20009:1</t>
-  </si>
-  <si>
-    <t>20010:1</t>
-  </si>
-  <si>
-    <t>20011:1</t>
-  </si>
-  <si>
-    <t>20012:1</t>
-  </si>
-  <si>
-    <t>20013:1</t>
-  </si>
-  <si>
-    <t>20014:1</t>
-  </si>
-  <si>
-    <t>20015:1</t>
-  </si>
-  <si>
-    <t>20016:1</t>
-  </si>
-  <si>
-    <t>20017:1</t>
-  </si>
-  <si>
-    <t>20018:1</t>
-  </si>
-  <si>
-    <t>20019:1</t>
-  </si>
-  <si>
-    <t>20020:1</t>
-  </si>
-  <si>
-    <t>20021:1</t>
-  </si>
-  <si>
-    <t>20022:1</t>
-  </si>
-  <si>
-    <t>20023:1</t>
-  </si>
-  <si>
-    <t>20024:1</t>
-  </si>
-  <si>
-    <t>20025:1</t>
-  </si>
-  <si>
-    <t>20026:1</t>
-  </si>
-  <si>
-    <t>20027:1</t>
-  </si>
-  <si>
-    <t>20028:1</t>
-  </si>
-  <si>
-    <t>20029:1</t>
-  </si>
-  <si>
-    <t>20030:1</t>
-  </si>
-  <si>
-    <t>20031:1</t>
-  </si>
-  <si>
-    <t>20032:1</t>
-  </si>
-  <si>
-    <t>20033:1</t>
-  </si>
-  <si>
-    <t>20034:1</t>
-  </si>
-  <si>
-    <t>20035:1</t>
-  </si>
-  <si>
-    <t>20036:1</t>
-  </si>
-  <si>
-    <t>20037:1</t>
-  </si>
-  <si>
-    <t>20038:1</t>
-  </si>
-  <si>
-    <t>20039:1</t>
-  </si>
-  <si>
-    <t>20040:1</t>
-  </si>
-  <si>
-    <t>20041:1</t>
-  </si>
-  <si>
-    <t>20042:1</t>
-  </si>
-  <si>
-    <t>20043:1</t>
-  </si>
-  <si>
-    <t>20044:1</t>
-  </si>
-  <si>
-    <t>20045:1</t>
-  </si>
-  <si>
-    <t>20046:1</t>
-  </si>
-  <si>
-    <t>20047:1</t>
-  </si>
-  <si>
-    <t>20048:1</t>
-  </si>
-  <si>
-    <t>20049:1</t>
-  </si>
-  <si>
-    <t>20050:1</t>
-  </si>
-  <si>
-    <t>20051:1</t>
-  </si>
-  <si>
-    <t>20052:1</t>
-  </si>
-  <si>
-    <t>20053:1</t>
-  </si>
-  <si>
-    <t>20054:1</t>
-  </si>
-  <si>
-    <t>20055:1</t>
-  </si>
-  <si>
-    <t>20056:1</t>
-  </si>
-  <si>
-    <t>20057:1</t>
-  </si>
-  <si>
-    <t>20058:1</t>
-  </si>
-  <si>
-    <t>20059:1</t>
-  </si>
-  <si>
-    <t>20060:1</t>
-  </si>
-  <si>
-    <t>20061:1</t>
-  </si>
-  <si>
-    <t>20062:1</t>
-  </si>
-  <si>
-    <t>20063:1</t>
-  </si>
-  <si>
-    <t>20064:1</t>
-  </si>
-  <si>
-    <t>20065:1</t>
-  </si>
-  <si>
-    <t>20066:1</t>
-  </si>
-  <si>
-    <t>20067:1</t>
-  </si>
-  <si>
-    <t>20068:1</t>
-  </si>
-  <si>
-    <t>20069:1</t>
-  </si>
-  <si>
-    <t>20070:1</t>
-  </si>
-  <si>
-    <t>20071:1</t>
-  </si>
-  <si>
-    <t>20072:1</t>
-  </si>
-  <si>
-    <t>20073:1</t>
-  </si>
-  <si>
-    <t>20074:1</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:11</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:11</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:3</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:12</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:12</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:4</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:13</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:13</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:5</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:14</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:14</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:6</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:15</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:15</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:7</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:16</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:16</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:8</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:17</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:17</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:9</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:18</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:18</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:10</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:19</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:19</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:11</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:20</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:20</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:12</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:21</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:21</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:13</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:22</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:22</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:14</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:23</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:23</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:15</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:24</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:24</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:16</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:25</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:25</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:17</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:26</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:26</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:18</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:27</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:27</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:19</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:28</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:28</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:20</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:29</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:29</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:21</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:30</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:30</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:22</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:31</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:31</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:23</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:32</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:32</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:24</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:33</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:33</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:25</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:34</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:34</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:26</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:35</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:35</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:27</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:36</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:36</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:28</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:37</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:37</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:29</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:38</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:38</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:30</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:39</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:39</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:31</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:40</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:40</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:32</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:41</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:41</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:33</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:42</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:42</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:34</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:43</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:43</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:35</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:44</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:44</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:36</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:45</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:45</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:37</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:46</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:46</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:38</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:47</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:47</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:39</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:48</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:48</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:40</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:49</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:49</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:41</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:50</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:50</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:42</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:51</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:51</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:43</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:52</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:52</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:44</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:53</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:53</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:45</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:54</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:54</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:46</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:55</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:55</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:47</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:56</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:56</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:48</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:57</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:57</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:49</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:58</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:58</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:50</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:59</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:59</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:51</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:60</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:60</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:52</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:61</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:61</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:53</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:62</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:62</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:54</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:63</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:63</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:55</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:64</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:64</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:56</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:65</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:65</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:57</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:66</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:66</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:58</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:67</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:67</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:59</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:68</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:68</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:60</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:69</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:69</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:61</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:70</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:70</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:62</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:71</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:71</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:63</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:72</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:72</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:64</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:73</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:73</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:65</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:74</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:74</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:66</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:75</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:75</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:67</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:76</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:76</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:68</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:77</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:77</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:69</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:78</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:78</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:70</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:79</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:79</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:71</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:80</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:80</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:72</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:81</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:81</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:73</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:82</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:82</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:74</t>
-  </si>
-  <si>
-    <t>0:100_1:10_2:10_3:10_4:10_5:83</t>
-  </si>
-  <si>
-    <t>1:10_2:10_3:10_4:10_5:83</t>
-  </si>
-  <si>
-    <t>1001811:1_3001811:75</t>
-  </si>
-  <si>
-    <t>1001112:1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2306,7 +2337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2353,6 +2384,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2651,7 +2685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N213"/>
+  <dimension ref="A1:N216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
@@ -8719,8 +8753,8 @@
       <c r="E139" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>39</v>
+      <c r="F139" s="19" t="s">
+        <v>682</v>
       </c>
       <c r="G139" s="19" t="s">
         <v>40</v>
@@ -8761,13 +8795,13 @@
         <v>39</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F140" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="G140" s="12" t="s">
-        <v>391</v>
+        <v>681</v>
+      </c>
+      <c r="F140" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="G140" s="26" t="s">
+        <v>689</v>
       </c>
       <c r="H140" s="12" t="s">
         <v>31</v>
@@ -8805,13 +8839,13 @@
         <v>39</v>
       </c>
       <c r="E141" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F141" t="s">
-        <v>392</v>
-      </c>
-      <c r="G141" t="s">
-        <v>392</v>
+        <v>681</v>
+      </c>
+      <c r="F141" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="G141" s="26" t="s">
+        <v>690</v>
       </c>
       <c r="H141" s="12" t="s">
         <v>31</v>
@@ -8826,13 +8860,13 @@
         <v>31</v>
       </c>
       <c r="L141" s="24" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="M141" s="24" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="N141" s="24" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.15">
@@ -8849,13 +8883,13 @@
         <v>39</v>
       </c>
       <c r="E142" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F142" t="s">
-        <v>393</v>
-      </c>
-      <c r="G142" t="s">
-        <v>393</v>
+        <v>681</v>
+      </c>
+      <c r="F142" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="G142" s="26" t="s">
+        <v>691</v>
       </c>
       <c r="H142" s="12" t="s">
         <v>31</v>
@@ -8870,13 +8904,13 @@
         <v>31</v>
       </c>
       <c r="L142" s="24" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="M142" s="24" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="N142" s="24" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.15">
@@ -8893,13 +8927,13 @@
         <v>39</v>
       </c>
       <c r="E143" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F143" t="s">
-        <v>394</v>
+        <v>681</v>
+      </c>
+      <c r="F143" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G143" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H143" s="12" t="s">
         <v>31</v>
@@ -8914,13 +8948,13 @@
         <v>31</v>
       </c>
       <c r="L143" s="24" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M143" s="24" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="N143" s="24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.15">
@@ -8937,13 +8971,13 @@
         <v>39</v>
       </c>
       <c r="E144" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F144" t="s">
-        <v>395</v>
+        <v>681</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G144" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H144" s="12" t="s">
         <v>31</v>
@@ -8958,13 +8992,13 @@
         <v>31</v>
       </c>
       <c r="L144" s="24" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M144" s="24" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="N144" s="24" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.15">
@@ -8981,13 +9015,13 @@
         <v>39</v>
       </c>
       <c r="E145" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F145" t="s">
-        <v>396</v>
+        <v>681</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G145" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H145" s="12" t="s">
         <v>31</v>
@@ -9002,13 +9036,13 @@
         <v>31</v>
       </c>
       <c r="L145" s="24" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="M145" s="24" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N145" s="24" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.15">
@@ -9025,13 +9059,13 @@
         <v>39</v>
       </c>
       <c r="E146" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F146" t="s">
-        <v>397</v>
+        <v>681</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G146" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H146" s="12" t="s">
         <v>31</v>
@@ -9046,13 +9080,13 @@
         <v>31</v>
       </c>
       <c r="L146" s="24" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M146" s="24" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="N146" s="24" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.15">
@@ -9069,13 +9103,13 @@
         <v>39</v>
       </c>
       <c r="E147" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F147" t="s">
-        <v>398</v>
+        <v>681</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G147" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H147" s="12" t="s">
         <v>31</v>
@@ -9090,13 +9124,13 @@
         <v>31</v>
       </c>
       <c r="L147" s="24" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="M147" s="24" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N147" s="24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.15">
@@ -9113,13 +9147,13 @@
         <v>39</v>
       </c>
       <c r="E148" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F148" t="s">
-        <v>399</v>
+        <v>681</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G148" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H148" s="12" t="s">
         <v>31</v>
@@ -9134,13 +9168,13 @@
         <v>31</v>
       </c>
       <c r="L148" s="24" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="M148" s="24" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="N148" s="24" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.15">
@@ -9157,13 +9191,13 @@
         <v>39</v>
       </c>
       <c r="E149" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F149" t="s">
-        <v>400</v>
+        <v>681</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G149" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H149" s="12" t="s">
         <v>31</v>
@@ -9178,13 +9212,13 @@
         <v>31</v>
       </c>
       <c r="L149" s="24" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="M149" s="24" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N149" s="24" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.15">
@@ -9201,13 +9235,13 @@
         <v>39</v>
       </c>
       <c r="E150" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F150" t="s">
-        <v>401</v>
+        <v>681</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G150" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H150" s="12" t="s">
         <v>31</v>
@@ -9222,13 +9256,13 @@
         <v>31</v>
       </c>
       <c r="L150" s="24" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="M150" s="24" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="N150" s="24" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.15">
@@ -9245,13 +9279,13 @@
         <v>39</v>
       </c>
       <c r="E151" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F151" t="s">
-        <v>402</v>
+        <v>681</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G151" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H151" s="12" t="s">
         <v>31</v>
@@ -9266,13 +9300,13 @@
         <v>31</v>
       </c>
       <c r="L151" s="24" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="M151" s="24" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N151" s="24" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.15">
@@ -9289,13 +9323,13 @@
         <v>39</v>
       </c>
       <c r="E152" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F152" t="s">
-        <v>403</v>
+        <v>681</v>
+      </c>
+      <c r="F152" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G152" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H152" s="12" t="s">
         <v>31</v>
@@ -9310,13 +9344,13 @@
         <v>31</v>
       </c>
       <c r="L152" s="24" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="M152" s="24" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="N152" s="24" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.15">
@@ -9333,13 +9367,13 @@
         <v>39</v>
       </c>
       <c r="E153" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F153" t="s">
-        <v>404</v>
+        <v>681</v>
+      </c>
+      <c r="F153" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G153" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H153" s="12" t="s">
         <v>31</v>
@@ -9354,13 +9388,13 @@
         <v>31</v>
       </c>
       <c r="L153" s="24" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="M153" s="24" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="N153" s="24" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.15">
@@ -9377,13 +9411,13 @@
         <v>39</v>
       </c>
       <c r="E154" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F154" t="s">
-        <v>405</v>
+        <v>681</v>
+      </c>
+      <c r="F154" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G154" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H154" s="12" t="s">
         <v>31</v>
@@ -9398,13 +9432,13 @@
         <v>31</v>
       </c>
       <c r="L154" s="24" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="M154" s="24" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="N154" s="24" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.15">
@@ -9421,13 +9455,13 @@
         <v>39</v>
       </c>
       <c r="E155" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F155" t="s">
-        <v>406</v>
+        <v>681</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G155" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H155" s="12" t="s">
         <v>31</v>
@@ -9442,13 +9476,13 @@
         <v>31</v>
       </c>
       <c r="L155" s="24" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="M155" s="24" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="N155" s="24" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.15">
@@ -9465,13 +9499,13 @@
         <v>39</v>
       </c>
       <c r="E156" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F156" t="s">
-        <v>407</v>
+        <v>681</v>
+      </c>
+      <c r="F156" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G156" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H156" s="12" t="s">
         <v>31</v>
@@ -9486,13 +9520,13 @@
         <v>31</v>
       </c>
       <c r="L156" s="24" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="M156" s="24" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="N156" s="24" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.15">
@@ -9509,13 +9543,13 @@
         <v>39</v>
       </c>
       <c r="E157" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F157" t="s">
-        <v>408</v>
+        <v>681</v>
+      </c>
+      <c r="F157" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G157" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H157" s="12" t="s">
         <v>31</v>
@@ -9530,13 +9564,13 @@
         <v>31</v>
       </c>
       <c r="L157" s="24" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="M157" s="24" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="N157" s="24" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.15">
@@ -9553,13 +9587,13 @@
         <v>39</v>
       </c>
       <c r="E158" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F158" t="s">
-        <v>409</v>
+        <v>681</v>
+      </c>
+      <c r="F158" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G158" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H158" s="12" t="s">
         <v>31</v>
@@ -9574,13 +9608,13 @@
         <v>31</v>
       </c>
       <c r="L158" s="24" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="M158" s="24" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="N158" s="24" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.15">
@@ -9597,13 +9631,13 @@
         <v>39</v>
       </c>
       <c r="E159" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F159" t="s">
-        <v>410</v>
+        <v>681</v>
+      </c>
+      <c r="F159" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G159" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H159" s="12" t="s">
         <v>31</v>
@@ -9618,13 +9652,13 @@
         <v>31</v>
       </c>
       <c r="L159" s="24" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M159" s="24" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="N159" s="24" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.15">
@@ -9641,13 +9675,13 @@
         <v>39</v>
       </c>
       <c r="E160" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F160" t="s">
-        <v>411</v>
+        <v>681</v>
+      </c>
+      <c r="F160" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G160" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H160" s="12" t="s">
         <v>31</v>
@@ -9662,13 +9696,13 @@
         <v>31</v>
       </c>
       <c r="L160" s="24" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="M160" s="24" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N160" s="24" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.15">
@@ -9685,13 +9719,13 @@
         <v>39</v>
       </c>
       <c r="E161" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F161" t="s">
-        <v>412</v>
+        <v>681</v>
+      </c>
+      <c r="F161" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G161" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="H161" s="12" t="s">
         <v>31</v>
@@ -9706,13 +9740,13 @@
         <v>31</v>
       </c>
       <c r="L161" s="24" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="M161" s="24" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="N161" s="24" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.15">
@@ -9729,13 +9763,13 @@
         <v>39</v>
       </c>
       <c r="E162" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F162" t="s">
-        <v>413</v>
+        <v>681</v>
+      </c>
+      <c r="F162" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G162" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H162" s="12" t="s">
         <v>31</v>
@@ -9750,13 +9784,13 @@
         <v>31</v>
       </c>
       <c r="L162" s="24" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="M162" s="24" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="N162" s="24" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.15">
@@ -9773,13 +9807,13 @@
         <v>39</v>
       </c>
       <c r="E163" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F163" t="s">
-        <v>414</v>
+        <v>681</v>
+      </c>
+      <c r="F163" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G163" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H163" s="12" t="s">
         <v>31</v>
@@ -9794,13 +9828,13 @@
         <v>31</v>
       </c>
       <c r="L163" s="24" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="M163" s="24" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="N163" s="24" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.15">
@@ -9817,13 +9851,13 @@
         <v>39</v>
       </c>
       <c r="E164" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F164" t="s">
-        <v>415</v>
+        <v>681</v>
+      </c>
+      <c r="F164" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G164" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H164" s="12" t="s">
         <v>31</v>
@@ -9838,13 +9872,13 @@
         <v>31</v>
       </c>
       <c r="L164" s="24" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="M164" s="24" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="N164" s="24" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.15">
@@ -9861,13 +9895,13 @@
         <v>39</v>
       </c>
       <c r="E165" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F165" t="s">
-        <v>416</v>
+        <v>681</v>
+      </c>
+      <c r="F165" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G165" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="H165" s="12" t="s">
         <v>31</v>
@@ -9882,13 +9916,13 @@
         <v>31</v>
       </c>
       <c r="L165" s="24" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="M165" s="24" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="N165" s="24" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.15">
@@ -9905,13 +9939,13 @@
         <v>39</v>
       </c>
       <c r="E166" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F166" t="s">
-        <v>417</v>
+        <v>681</v>
+      </c>
+      <c r="F166" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G166" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H166" s="12" t="s">
         <v>31</v>
@@ -9926,13 +9960,13 @@
         <v>31</v>
       </c>
       <c r="L166" s="24" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="M166" s="24" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="N166" s="24" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.15">
@@ -9949,13 +9983,13 @@
         <v>39</v>
       </c>
       <c r="E167" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F167" t="s">
-        <v>418</v>
+        <v>681</v>
+      </c>
+      <c r="F167" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G167" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H167" s="12" t="s">
         <v>31</v>
@@ -9970,13 +10004,13 @@
         <v>31</v>
       </c>
       <c r="L167" s="24" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="M167" s="24" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="N167" s="24" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.15">
@@ -9993,13 +10027,13 @@
         <v>39</v>
       </c>
       <c r="E168" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F168" t="s">
-        <v>419</v>
+        <v>681</v>
+      </c>
+      <c r="F168" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G168" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="H168" s="12" t="s">
         <v>31</v>
@@ -10014,13 +10048,13 @@
         <v>31</v>
       </c>
       <c r="L168" s="24" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="M168" s="24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="N168" s="24" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.15">
@@ -10037,13 +10071,13 @@
         <v>39</v>
       </c>
       <c r="E169" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F169" t="s">
-        <v>420</v>
+        <v>681</v>
+      </c>
+      <c r="F169" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G169" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H169" s="12" t="s">
         <v>31</v>
@@ -10058,13 +10092,13 @@
         <v>31</v>
       </c>
       <c r="L169" s="24" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="M169" s="24" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="N169" s="24" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.15">
@@ -10081,13 +10115,13 @@
         <v>39</v>
       </c>
       <c r="E170" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F170" t="s">
-        <v>421</v>
+        <v>681</v>
+      </c>
+      <c r="F170" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G170" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H170" s="12" t="s">
         <v>31</v>
@@ -10102,13 +10136,13 @@
         <v>31</v>
       </c>
       <c r="L170" s="24" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="M170" s="24" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="N170" s="24" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.15">
@@ -10125,13 +10159,13 @@
         <v>39</v>
       </c>
       <c r="E171" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F171" t="s">
-        <v>422</v>
+        <v>681</v>
+      </c>
+      <c r="F171" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G171" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H171" s="12" t="s">
         <v>31</v>
@@ -10146,13 +10180,13 @@
         <v>31</v>
       </c>
       <c r="L171" s="24" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="M171" s="24" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="N171" s="24" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.15">
@@ -10169,13 +10203,13 @@
         <v>39</v>
       </c>
       <c r="E172" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F172" t="s">
-        <v>423</v>
+        <v>681</v>
+      </c>
+      <c r="F172" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G172" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H172" s="12" t="s">
         <v>31</v>
@@ -10190,13 +10224,13 @@
         <v>31</v>
       </c>
       <c r="L172" s="24" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="M172" s="24" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="N172" s="24" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.15">
@@ -10213,13 +10247,13 @@
         <v>39</v>
       </c>
       <c r="E173" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F173" t="s">
-        <v>424</v>
+        <v>681</v>
+      </c>
+      <c r="F173" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G173" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H173" s="12" t="s">
         <v>31</v>
@@ -10234,13 +10268,13 @@
         <v>31</v>
       </c>
       <c r="L173" s="24" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="M173" s="24" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N173" s="24" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.15">
@@ -10257,13 +10291,13 @@
         <v>39</v>
       </c>
       <c r="E174" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F174" t="s">
-        <v>425</v>
+        <v>681</v>
+      </c>
+      <c r="F174" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G174" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H174" s="12" t="s">
         <v>31</v>
@@ -10278,13 +10312,13 @@
         <v>31</v>
       </c>
       <c r="L174" s="24" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M174" s="24" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="N174" s="24" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.15">
@@ -10301,13 +10335,13 @@
         <v>39</v>
       </c>
       <c r="E175" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F175" t="s">
-        <v>426</v>
+        <v>681</v>
+      </c>
+      <c r="F175" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G175" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H175" s="12" t="s">
         <v>31</v>
@@ -10322,13 +10356,13 @@
         <v>31</v>
       </c>
       <c r="L175" s="24" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="M175" s="24" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="N175" s="24" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.15">
@@ -10345,13 +10379,13 @@
         <v>39</v>
       </c>
       <c r="E176" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F176" t="s">
-        <v>427</v>
+        <v>681</v>
+      </c>
+      <c r="F176" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G176" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H176" s="12" t="s">
         <v>31</v>
@@ -10366,13 +10400,13 @@
         <v>31</v>
       </c>
       <c r="L176" s="24" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="M176" s="24" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="N176" s="24" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.15">
@@ -10389,13 +10423,13 @@
         <v>39</v>
       </c>
       <c r="E177" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F177" t="s">
-        <v>428</v>
+        <v>681</v>
+      </c>
+      <c r="F177" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G177" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H177" s="12" t="s">
         <v>31</v>
@@ -10410,13 +10444,13 @@
         <v>31</v>
       </c>
       <c r="L177" s="24" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M177" s="24" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N177" s="24" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.15">
@@ -10433,13 +10467,13 @@
         <v>39</v>
       </c>
       <c r="E178" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F178" t="s">
-        <v>429</v>
+        <v>681</v>
+      </c>
+      <c r="F178" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G178" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H178" s="12" t="s">
         <v>31</v>
@@ -10454,13 +10488,13 @@
         <v>31</v>
       </c>
       <c r="L178" s="24" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="M178" s="24" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="N178" s="24" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.15">
@@ -10477,13 +10511,13 @@
         <v>39</v>
       </c>
       <c r="E179" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F179" t="s">
-        <v>430</v>
+        <v>681</v>
+      </c>
+      <c r="F179" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G179" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H179" s="12" t="s">
         <v>31</v>
@@ -10498,13 +10532,13 @@
         <v>31</v>
       </c>
       <c r="L179" s="24" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="M179" s="24" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="N179" s="24" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.15">
@@ -10521,13 +10555,13 @@
         <v>39</v>
       </c>
       <c r="E180" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F180" t="s">
-        <v>431</v>
+        <v>681</v>
+      </c>
+      <c r="F180" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G180" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H180" s="12" t="s">
         <v>31</v>
@@ -10542,13 +10576,13 @@
         <v>31</v>
       </c>
       <c r="L180" s="24" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="M180" s="24" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="N180" s="24" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.15">
@@ -10565,13 +10599,13 @@
         <v>39</v>
       </c>
       <c r="E181" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F181" t="s">
-        <v>432</v>
+        <v>681</v>
+      </c>
+      <c r="F181" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G181" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H181" s="12" t="s">
         <v>31</v>
@@ -10586,13 +10620,13 @@
         <v>31</v>
       </c>
       <c r="L181" s="24" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="M181" s="24" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="N181" s="24" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.15">
@@ -10609,13 +10643,13 @@
         <v>39</v>
       </c>
       <c r="E182" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F182" t="s">
-        <v>433</v>
+        <v>681</v>
+      </c>
+      <c r="F182" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G182" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H182" s="12" t="s">
         <v>31</v>
@@ -10630,13 +10664,13 @@
         <v>31</v>
       </c>
       <c r="L182" s="24" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="M182" s="24" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="N182" s="24" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.15">
@@ -10653,13 +10687,13 @@
         <v>39</v>
       </c>
       <c r="E183" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F183" t="s">
-        <v>434</v>
+        <v>681</v>
+      </c>
+      <c r="F183" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G183" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H183" s="12" t="s">
         <v>31</v>
@@ -10674,13 +10708,13 @@
         <v>31</v>
       </c>
       <c r="L183" s="24" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M183" s="24" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="N183" s="24" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.15">
@@ -10697,13 +10731,13 @@
         <v>39</v>
       </c>
       <c r="E184" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F184" t="s">
-        <v>435</v>
+        <v>681</v>
+      </c>
+      <c r="F184" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G184" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H184" s="12" t="s">
         <v>31</v>
@@ -10718,13 +10752,13 @@
         <v>31</v>
       </c>
       <c r="L184" s="24" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="M184" s="24" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="N184" s="24" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.15">
@@ -10741,13 +10775,13 @@
         <v>39</v>
       </c>
       <c r="E185" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F185" t="s">
-        <v>436</v>
+        <v>681</v>
+      </c>
+      <c r="F185" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G185" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H185" s="12" t="s">
         <v>31</v>
@@ -10762,13 +10796,13 @@
         <v>31</v>
       </c>
       <c r="L185" s="24" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="M185" s="24" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="N185" s="24" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.15">
@@ -10785,13 +10819,13 @@
         <v>39</v>
       </c>
       <c r="E186" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F186" t="s">
-        <v>437</v>
+        <v>681</v>
+      </c>
+      <c r="F186" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G186" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H186" s="12" t="s">
         <v>31</v>
@@ -10806,13 +10840,13 @@
         <v>31</v>
       </c>
       <c r="L186" s="24" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="M186" s="24" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="N186" s="24" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.15">
@@ -10829,13 +10863,13 @@
         <v>39</v>
       </c>
       <c r="E187" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F187" t="s">
-        <v>438</v>
+        <v>681</v>
+      </c>
+      <c r="F187" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G187" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H187" s="12" t="s">
         <v>31</v>
@@ -10850,13 +10884,13 @@
         <v>31</v>
       </c>
       <c r="L187" s="24" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="M187" s="24" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="N187" s="24" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.15">
@@ -10873,13 +10907,13 @@
         <v>39</v>
       </c>
       <c r="E188" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F188" t="s">
-        <v>439</v>
+        <v>681</v>
+      </c>
+      <c r="F188" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G188" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H188" s="12" t="s">
         <v>31</v>
@@ -10894,13 +10928,13 @@
         <v>31</v>
       </c>
       <c r="L188" s="24" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="M188" s="24" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="N188" s="24" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.15">
@@ -10917,13 +10951,13 @@
         <v>39</v>
       </c>
       <c r="E189" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F189" t="s">
-        <v>440</v>
+        <v>681</v>
+      </c>
+      <c r="F189" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G189" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H189" s="12" t="s">
         <v>31</v>
@@ -10938,13 +10972,13 @@
         <v>31</v>
       </c>
       <c r="L189" s="24" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M189" s="24" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="N189" s="24" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.15">
@@ -10961,13 +10995,13 @@
         <v>39</v>
       </c>
       <c r="E190" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F190" t="s">
-        <v>441</v>
+        <v>681</v>
+      </c>
+      <c r="F190" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G190" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H190" s="12" t="s">
         <v>31</v>
@@ -10982,13 +11016,13 @@
         <v>31</v>
       </c>
       <c r="L190" s="24" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M190" s="24" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="N190" s="24" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.15">
@@ -11005,13 +11039,13 @@
         <v>39</v>
       </c>
       <c r="E191" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F191" t="s">
-        <v>442</v>
+        <v>681</v>
+      </c>
+      <c r="F191" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G191" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="H191" s="12" t="s">
         <v>31</v>
@@ -11026,13 +11060,13 @@
         <v>31</v>
       </c>
       <c r="L191" s="24" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M191" s="24" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N191" s="24" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.15">
@@ -11049,13 +11083,13 @@
         <v>39</v>
       </c>
       <c r="E192" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F192" t="s">
-        <v>443</v>
+        <v>681</v>
+      </c>
+      <c r="F192" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G192" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H192" s="12" t="s">
         <v>31</v>
@@ -11070,13 +11104,13 @@
         <v>31</v>
       </c>
       <c r="L192" s="24" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="M192" s="24" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="N192" s="24" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.15">
@@ -11093,13 +11127,13 @@
         <v>39</v>
       </c>
       <c r="E193" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F193" t="s">
-        <v>444</v>
+        <v>681</v>
+      </c>
+      <c r="F193" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G193" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H193" s="12" t="s">
         <v>31</v>
@@ -11114,13 +11148,13 @@
         <v>31</v>
       </c>
       <c r="L193" s="24" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="M193" s="24" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="N193" s="24" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.15">
@@ -11137,13 +11171,13 @@
         <v>39</v>
       </c>
       <c r="E194" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F194" t="s">
-        <v>445</v>
+        <v>681</v>
+      </c>
+      <c r="F194" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G194" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H194" s="12" t="s">
         <v>31</v>
@@ -11158,13 +11192,13 @@
         <v>31</v>
       </c>
       <c r="L194" s="24" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="M194" s="24" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="N194" s="24" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.15">
@@ -11181,13 +11215,13 @@
         <v>39</v>
       </c>
       <c r="E195" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F195" t="s">
-        <v>446</v>
+        <v>681</v>
+      </c>
+      <c r="F195" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G195" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H195" s="12" t="s">
         <v>31</v>
@@ -11202,13 +11236,13 @@
         <v>31</v>
       </c>
       <c r="L195" s="24" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="M195" s="24" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N195" s="24" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.15">
@@ -11225,13 +11259,13 @@
         <v>39</v>
       </c>
       <c r="E196" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F196" t="s">
-        <v>447</v>
+        <v>681</v>
+      </c>
+      <c r="F196" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G196" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H196" s="12" t="s">
         <v>31</v>
@@ -11246,13 +11280,13 @@
         <v>31</v>
       </c>
       <c r="L196" s="24" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="M196" s="24" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="N196" s="24" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.15">
@@ -11269,13 +11303,13 @@
         <v>39</v>
       </c>
       <c r="E197" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F197" t="s">
-        <v>448</v>
+        <v>681</v>
+      </c>
+      <c r="F197" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G197" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H197" s="12" t="s">
         <v>31</v>
@@ -11290,13 +11324,13 @@
         <v>31</v>
       </c>
       <c r="L197" s="24" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="M197" s="24" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="N197" s="24" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.15">
@@ -11313,13 +11347,13 @@
         <v>39</v>
       </c>
       <c r="E198" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F198" t="s">
-        <v>449</v>
+        <v>681</v>
+      </c>
+      <c r="F198" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G198" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H198" s="12" t="s">
         <v>31</v>
@@ -11334,13 +11368,13 @@
         <v>31</v>
       </c>
       <c r="L198" s="24" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M198" s="24" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="N198" s="24" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.15">
@@ -11357,13 +11391,13 @@
         <v>39</v>
       </c>
       <c r="E199" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F199" t="s">
-        <v>450</v>
+        <v>681</v>
+      </c>
+      <c r="F199" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G199" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H199" s="12" t="s">
         <v>31</v>
@@ -11378,13 +11412,13 @@
         <v>31</v>
       </c>
       <c r="L199" s="24" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="M199" s="24" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="N199" s="24" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.15">
@@ -11401,13 +11435,13 @@
         <v>39</v>
       </c>
       <c r="E200" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F200" t="s">
-        <v>451</v>
+        <v>681</v>
+      </c>
+      <c r="F200" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G200" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H200" s="12" t="s">
         <v>31</v>
@@ -11422,13 +11456,13 @@
         <v>31</v>
       </c>
       <c r="L200" s="24" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="M200" s="24" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="N200" s="24" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.15">
@@ -11445,13 +11479,13 @@
         <v>39</v>
       </c>
       <c r="E201" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F201" t="s">
-        <v>452</v>
+        <v>681</v>
+      </c>
+      <c r="F201" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G201" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H201" s="12" t="s">
         <v>31</v>
@@ -11466,13 +11500,13 @@
         <v>31</v>
       </c>
       <c r="L201" s="24" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="M201" s="24" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N201" s="24" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.15">
@@ -11489,13 +11523,13 @@
         <v>39</v>
       </c>
       <c r="E202" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F202" t="s">
-        <v>453</v>
+        <v>681</v>
+      </c>
+      <c r="F202" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G202" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H202" s="12" t="s">
         <v>31</v>
@@ -11510,13 +11544,13 @@
         <v>31</v>
       </c>
       <c r="L202" s="24" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="M202" s="24" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="N202" s="24" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.15">
@@ -11533,13 +11567,13 @@
         <v>39</v>
       </c>
       <c r="E203" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F203" t="s">
-        <v>454</v>
+        <v>681</v>
+      </c>
+      <c r="F203" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G203" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H203" s="12" t="s">
         <v>31</v>
@@ -11554,13 +11588,13 @@
         <v>31</v>
       </c>
       <c r="L203" s="24" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="M203" s="24" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="N203" s="24" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.15">
@@ -11577,13 +11611,13 @@
         <v>39</v>
       </c>
       <c r="E204" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F204" t="s">
-        <v>455</v>
+        <v>681</v>
+      </c>
+      <c r="F204" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G204" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H204" s="12" t="s">
         <v>31</v>
@@ -11598,13 +11632,13 @@
         <v>31</v>
       </c>
       <c r="L204" s="24" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="M204" s="24" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="N204" s="24" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.15">
@@ -11621,13 +11655,13 @@
         <v>39</v>
       </c>
       <c r="E205" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F205" t="s">
-        <v>456</v>
+        <v>681</v>
+      </c>
+      <c r="F205" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G205" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H205" s="12" t="s">
         <v>31</v>
@@ -11642,13 +11676,13 @@
         <v>31</v>
       </c>
       <c r="L205" s="24" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="M205" s="24" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="N205" s="24" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.15">
@@ -11665,13 +11699,13 @@
         <v>39</v>
       </c>
       <c r="E206" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F206" t="s">
-        <v>457</v>
+        <v>681</v>
+      </c>
+      <c r="F206" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G206" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H206" s="12" t="s">
         <v>31</v>
@@ -11686,13 +11720,13 @@
         <v>31</v>
       </c>
       <c r="L206" s="24" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M206" s="24" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="N206" s="24" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.15">
@@ -11709,13 +11743,13 @@
         <v>39</v>
       </c>
       <c r="E207" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F207" t="s">
-        <v>458</v>
+        <v>681</v>
+      </c>
+      <c r="F207" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G207" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H207" s="12" t="s">
         <v>31</v>
@@ -11730,13 +11764,13 @@
         <v>31</v>
       </c>
       <c r="L207" s="24" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="M207" s="24" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="N207" s="24" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.15">
@@ -11753,13 +11787,13 @@
         <v>39</v>
       </c>
       <c r="E208" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F208" t="s">
-        <v>459</v>
+        <v>681</v>
+      </c>
+      <c r="F208" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G208" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H208" s="12" t="s">
         <v>31</v>
@@ -11774,13 +11808,13 @@
         <v>31</v>
       </c>
       <c r="L208" s="24" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="M208" s="24" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="N208" s="24" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.15">
@@ -11797,13 +11831,13 @@
         <v>39</v>
       </c>
       <c r="E209" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F209" t="s">
-        <v>460</v>
+        <v>681</v>
+      </c>
+      <c r="F209" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G209" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H209" s="12" t="s">
         <v>31</v>
@@ -11818,13 +11852,13 @@
         <v>31</v>
       </c>
       <c r="L209" s="24" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="M209" s="24" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="N209" s="24" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.15">
@@ -11841,13 +11875,13 @@
         <v>39</v>
       </c>
       <c r="E210" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F210" t="s">
-        <v>461</v>
+        <v>681</v>
+      </c>
+      <c r="F210" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G210" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H210" s="12" t="s">
         <v>31</v>
@@ -11862,13 +11896,13 @@
         <v>31</v>
       </c>
       <c r="L210" s="24" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="M210" s="24" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="N210" s="24" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.15">
@@ -11885,13 +11919,13 @@
         <v>39</v>
       </c>
       <c r="E211" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F211" t="s">
-        <v>462</v>
+        <v>681</v>
+      </c>
+      <c r="F211" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G211" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="H211" s="12" t="s">
         <v>31</v>
@@ -11906,13 +11940,13 @@
         <v>31</v>
       </c>
       <c r="L211" s="24" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="M211" s="24" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="N211" s="24" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.15">
@@ -11929,13 +11963,13 @@
         <v>39</v>
       </c>
       <c r="E212" s="22" t="s">
-        <v>684</v>
-      </c>
-      <c r="F212" t="s">
-        <v>463</v>
+        <v>681</v>
+      </c>
+      <c r="F212" s="28" t="s">
+        <v>682</v>
       </c>
       <c r="G212" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H212" s="12" t="s">
         <v>31</v>
@@ -11950,13 +11984,13 @@
         <v>31</v>
       </c>
       <c r="L212" s="24" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="M212" s="24" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="N212" s="24" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.15">
@@ -11973,34 +12007,166 @@
         <v>39</v>
       </c>
       <c r="E213" s="22" t="s">
+        <v>681</v>
+      </c>
+      <c r="F213" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="G213" t="s">
+        <v>461</v>
+      </c>
+      <c r="H213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K213" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L213" s="24" t="s">
+        <v>678</v>
+      </c>
+      <c r="M213" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="N213" s="24" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A214">
+        <v>220</v>
+      </c>
+      <c r="B214" s="26" t="s">
+        <v>686</v>
+      </c>
+      <c r="C214" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F214" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="G214" s="19" t="s">
+        <v>683</v>
+      </c>
+      <c r="H214" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I214" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K214" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L214" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="M214" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="N214" s="24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A215">
+        <v>221</v>
+      </c>
+      <c r="B215" s="26" t="s">
+        <v>687</v>
+      </c>
+      <c r="C215" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F215" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="G215" s="19" t="s">
         <v>684</v>
       </c>
-      <c r="F213" t="s">
-        <v>464</v>
-      </c>
-      <c r="G213" t="s">
-        <v>464</v>
-      </c>
-      <c r="H213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K213" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="L213" s="24" t="s">
-        <v>681</v>
-      </c>
-      <c r="M213" s="24" t="s">
+      <c r="H215" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I215" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K215" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L215" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="M215" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="N215" s="24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A216">
+        <v>222</v>
+      </c>
+      <c r="B216" s="26" t="s">
+        <v>688</v>
+      </c>
+      <c r="C216" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F216" s="19" t="s">
         <v>682</v>
       </c>
-      <c r="N213" s="24" t="s">
-        <v>683</v>
+      <c r="G216" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="H216" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I216" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K216" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L216" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="M216" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="N216" s="24" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
